--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 55708-2023</t>
+          <t>A 26989-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45239</v>
+        <v>45811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1523,273 +1523,273 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Nötkråka
+Kungsfågel
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 55708-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Talltita
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 15249-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>46105</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>2.4</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Kornknutmossa
 Smal svampklubba
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 26989-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45811</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Nötkråka
-Kungsfågel
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 9491-2025</t>
+          <t>A 63592-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45715</v>
+        <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1860,42 +1860,42 @@
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
-Revlummer</t>
+Vanlig padda</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55274-2025</t>
+          <t>A 9491-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45968</v>
+        <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="I14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1965,149 +1965,149 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Stor revmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 55274-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Skuggmossa
 Trådticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 63592-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44508</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 27676-2026</t>
+          <t>A 34938-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46190</v>
+        <v>44796</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2137,20 +2137,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2173,146 +2173,146 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27676-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 34938-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44796</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45740</v>
+        <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2584,10 +2584,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2600,42 +2600,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45587</v>
+        <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2665,17 +2665,17 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2705,42 +2705,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2750,14 +2750,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45239</v>
+        <v>44697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2803,53 +2803,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2863,10 +2859,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45175</v>
+        <v>45813</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2879,7 +2875,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>14.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2919,42 +2915,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2968,10 +2964,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46163</v>
+        <v>45740</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,23 +2980,23 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
@@ -3008,10 +3004,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3024,42 +3020,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3069,14 +3065,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44697</v>
+        <v>45239</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,7 +3085,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3122,49 +3118,53 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21398-2023</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45063</v>
+        <v>46163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 21398-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44902</v>
+        <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3343,38 +3343,38 @@
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45224</v>
+        <v>45587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,13 +3404,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3444,42 +3444,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45813</v>
+        <v>45224</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,16 +3509,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>14.1</v>
+        <v>5.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3549,35 +3549,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45281</v>
+        <v>44873</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
         <v>45219</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45377</v>
+        <v>45651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45393</v>
+        <v>45798</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45219</v>
+        <v>45704</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45219</v>
+        <v>45715</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45313</v>
+        <v>45715</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44873</v>
+        <v>45811</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45895</v>
+        <v>45813</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5146,13 +5146,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5195,7 +5190,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5209,10 +5204,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45895</v>
+        <v>45629</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5225,7 +5220,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5268,7 +5263,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5282,10 +5277,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45219</v>
+        <v>45373</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5298,7 +5293,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5341,7 +5336,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5355,10 +5350,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45168</v>
+        <v>45895</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5371,7 +5366,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5414,7 +5409,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5428,10 +5423,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44960</v>
+        <v>45895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,8 +5438,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5487,7 +5487,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45012</v>
+        <v>45625</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45751</v>
+        <v>45219</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44732</v>
+        <v>45219</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45925</v>
+        <v>45012</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44733</v>
+        <v>45925</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45935</v>
+        <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45936</v>
+        <v>45168</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45934</v>
+        <v>45751</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45754</v>
+        <v>45935</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45686</v>
+        <v>45934</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45587</v>
+        <v>45686</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6307,7 +6307,7 @@
         <v>45950</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46098</v>
+        <v>45107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45705</v>
+        <v>44573</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44826</v>
+        <v>45002</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>11.5</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46107</v>
+        <v>44532</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46107</v>
+        <v>46098</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46107</v>
+        <v>45705</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6818,7 +6818,7 @@
         <v>46106</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45968</v>
+        <v>46107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45560</v>
+        <v>46107</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45058</v>
+        <v>46107</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45994</v>
+        <v>44911</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45704</v>
+        <v>45560</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45715</v>
+        <v>45968</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45715</v>
+        <v>45754</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45140</v>
+        <v>44733</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7475,7 +7475,7 @@
         <v>45747</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7548,7 +7548,7 @@
         <v>46002</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44532</v>
+        <v>45994</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7694,7 +7694,7 @@
         <v>46002</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7767,7 +7767,7 @@
         <v>44547</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45315</v>
+        <v>45107</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45377</v>
+        <v>45587</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45608</v>
+        <v>45336</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45629</v>
+        <v>44826</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>11.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45107</v>
+        <v>46072</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44721</v>
+        <v>45855</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45167</v>
+        <v>46238</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45583</v>
+        <v>46238</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46072</v>
+        <v>46238</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45855</v>
+        <v>45167</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8563,14 +8563,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45287</v>
+        <v>46212</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45321</v>
+        <v>46212</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45307</v>
+        <v>45167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44908</v>
+        <v>45608</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45167</v>
+        <v>45587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46238</v>
+        <v>45393</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45651</v>
+        <v>46225</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9147,14 +9147,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44732</v>
+        <v>45315</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44784</v>
+        <v>45324</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45336</v>
+        <v>46230</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46212</v>
+        <v>46269</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45280</v>
+        <v>45336</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46212</v>
+        <v>44721</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9648,7 +9648,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45587</v>
+        <v>45281</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45324</v>
+        <v>45321</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44573</v>
+        <v>45307</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9881,10 +9881,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45218</v>
+        <v>44732</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,13 +9896,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9945,7 +9940,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9959,10 +9954,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45244</v>
+        <v>44960</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9975,7 +9970,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10018,7 +10013,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10032,10 +10027,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44911</v>
+        <v>45219</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10048,7 +10043,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10091,7 +10086,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10105,10 +10100,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45002</v>
+        <v>45219</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10121,7 +10116,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10164,7 +10159,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10178,10 +10173,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45107</v>
+        <v>45313</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10194,7 +10189,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10237,7 +10232,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10251,10 +10246,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46223</v>
+        <v>45140</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10267,7 +10262,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10310,7 +10305,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10324,10 +10319,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45336</v>
+        <v>44784</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10340,7 +10335,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10383,7 +10378,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10393,14 +10388,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46225</v>
+        <v>45287</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10456,7 +10451,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10466,14 +10461,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46225</v>
+        <v>44908</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10486,7 +10481,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10529,7 +10524,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10539,14 +10534,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45237</v>
+        <v>45377</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10559,7 +10554,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10602,7 +10597,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10616,10 +10611,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46269</v>
+        <v>45058</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10632,7 +10627,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10675,7 +10670,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10685,14 +10680,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45219</v>
+        <v>45237</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10705,7 +10700,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10748,7 +10743,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10762,10 +10757,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46230</v>
+        <v>45224</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10778,7 +10773,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10821,7 +10816,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10835,10 +10830,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45224</v>
+        <v>45244</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10851,7 +10846,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10894,7 +10889,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10908,10 +10903,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45785</v>
+        <v>45377</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10924,7 +10919,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10967,7 +10962,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10981,10 +10976,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45798</v>
+        <v>45218</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10996,8 +10991,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45811</v>
+        <v>45280</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45813</v>
+        <v>44732</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45373</v>
+        <v>45583</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45625</v>
+        <v>45785</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37201-2023</t>
+          <t>A 55708-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45155</v>
+        <v>45239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1410,386 +1410,386 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37201-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sexfläckig bastardsvärmare
 Slåttergubbe
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 15249-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Kornknutmossa
+Smal svampklubba
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 26989-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>45811</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>4.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Nötkråka
 Kungsfågel
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 55708-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 15249-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Kornknutmossa
-Smal svampklubba
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 63592-2021</t>
+          <t>A 55274-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44508</v>
+        <v>45968</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1859,460 +1859,460 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Skuggmossa
+Trådticka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 27676-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 63592-2021</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44508</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Stor revmossa
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 34938-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44796</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 9491-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45715</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>1.5</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 55274-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45968</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmossa
-Trådticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 34938-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44796</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27676-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44902</v>
+        <v>45239</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2593,49 +2593,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2649,10 +2653,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45175</v>
+        <v>45587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2665,16 +2669,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2689,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2705,42 +2709,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 21398-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2750,14 +2754,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44697</v>
+        <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2770,7 +2774,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2814,38 +2818,38 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2859,10 +2863,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45813</v>
+        <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2875,16 +2879,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>14.1</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2899,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2915,42 +2919,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2964,10 +2968,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45740</v>
+        <v>45175</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2980,7 +2984,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2989,13 +2993,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3007,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3020,42 +3024,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3069,10 +3073,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45239</v>
+        <v>44902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3085,7 +3089,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3118,53 +3122,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46163</v>
+        <v>44697</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21398-2023</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45063</v>
+        <v>45224</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3339,42 +3339,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45587</v>
+        <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>14.1</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3444,42 +3444,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45224</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,23 +3509,23 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
@@ -3533,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3549,35 +3549,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 71648-2021</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44543</v>
+        <v>45377</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19782-2022</t>
+          <t>A 71648-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44694</v>
+        <v>44543</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63595-2021</t>
+          <t>A 19782-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4470,14 +4470,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44508</v>
+        <v>44694</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4533,7 +4533,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44873</v>
+        <v>45393</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51162-2023</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4623,7 +4623,7 @@
         <v>45219</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45651</v>
+        <v>45219</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 63595-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45798</v>
+        <v>44508</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 51162-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45704</v>
+        <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45715</v>
+        <v>45281</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4981,14 +4981,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45715</v>
+        <v>45287</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45811</v>
+        <v>45686</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45813</v>
+        <v>45313</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45629</v>
+        <v>45321</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45373</v>
+        <v>45307</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45895</v>
+        <v>44873</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45895</v>
+        <v>44908</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5438,13 +5438,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5487,7 +5482,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5501,10 +5496,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45625</v>
+        <v>45895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,8 +5511,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45219</v>
+        <v>45895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45219</v>
+        <v>45167</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45012</v>
+        <v>46098</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45925</v>
+        <v>45705</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45936</v>
+        <v>45012</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45168</v>
+        <v>46107</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45751</v>
+        <v>46107</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45935</v>
+        <v>46107</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6154,14 +6154,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45934</v>
+        <v>46106</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45686</v>
+        <v>45651</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45950</v>
+        <v>45925</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45107</v>
+        <v>45560</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44573</v>
+        <v>45935</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45002</v>
+        <v>45936</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44532</v>
+        <v>45934</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46098</v>
+        <v>45950</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45705</v>
+        <v>45219</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6811,14 +6811,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46106</v>
+        <v>45168</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46107</v>
+        <v>44960</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46107</v>
+        <v>45747</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46107</v>
+        <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44911</v>
+        <v>45968</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45560</v>
+        <v>44732</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45968</v>
+        <v>44733</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45754</v>
+        <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44733</v>
+        <v>44547</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45747</v>
+        <v>45754</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46002</v>
+        <v>45587</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7621,7 +7621,7 @@
         <v>45994</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46002</v>
+        <v>44826</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>11.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44547</v>
+        <v>45704</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45107</v>
+        <v>44732</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45587</v>
+        <v>45715</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45336</v>
+        <v>45715</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44826</v>
+        <v>45058</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>11.5</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8132,7 +8132,7 @@
         <v>46072</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45855</v>
+        <v>44784</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46238</v>
+        <v>45855</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46238</v>
+        <v>45140</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46238</v>
+        <v>45336</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45167</v>
+        <v>44532</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46212</v>
+        <v>45280</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46212</v>
+        <v>45587</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45167</v>
+        <v>45315</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45608</v>
+        <v>45324</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45587</v>
+        <v>44573</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45393</v>
+        <v>45377</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46223</v>
+        <v>45608</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46225</v>
+        <v>45218</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,8 +9093,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9137,7 +9142,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9147,14 +9152,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46225</v>
+        <v>45629</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9167,7 +9172,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9210,7 +9215,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9224,10 +9229,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45315</v>
+        <v>45244</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9245,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9283,7 +9288,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9297,10 +9302,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45324</v>
+        <v>44911</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9356,7 +9361,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9370,10 +9375,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46230</v>
+        <v>45002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9391,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9429,7 +9434,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,10 +9448,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46269</v>
+        <v>45107</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9464,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9502,7 +9507,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9516,10 +9521,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45336</v>
+        <v>46212</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9532,7 +9537,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9575,7 +9580,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9589,10 +9594,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44721</v>
+        <v>45107</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9610,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9648,7 +9653,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9662,10 +9667,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45281</v>
+        <v>44721</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9678,7 +9683,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9721,7 +9726,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9735,10 +9740,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45321</v>
+        <v>45167</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9751,7 +9756,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9794,7 +9799,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9808,10 +9813,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45307</v>
+        <v>46212</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9824,7 +9829,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9867,7 +9872,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9881,10 +9886,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44732</v>
+        <v>45583</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,7 +9902,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9940,7 +9945,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9954,10 +9959,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44960</v>
+        <v>45336</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9970,7 +9975,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10013,7 +10018,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10023,14 +10028,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45219</v>
+        <v>45237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10043,7 +10048,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10086,7 +10091,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10100,10 +10105,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45219</v>
+        <v>46223</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10159,7 +10164,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10173,10 +10178,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45313</v>
+        <v>46225</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10189,7 +10194,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10232,7 +10237,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10242,14 +10247,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45140</v>
+        <v>46225</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10262,7 +10267,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10305,7 +10310,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10319,10 +10324,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44784</v>
+        <v>45219</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10335,7 +10340,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10378,7 +10383,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10388,14 +10393,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45287</v>
+        <v>46269</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10408,7 +10413,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10451,7 +10456,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10465,10 +10470,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44908</v>
+        <v>46230</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10481,7 +10486,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10524,7 +10529,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10538,10 +10543,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45377</v>
+        <v>45224</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10554,7 +10559,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10597,7 +10602,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10611,10 +10616,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45058</v>
+        <v>46238</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10627,7 +10632,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10670,7 +10675,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10680,14 +10685,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45237</v>
+        <v>46238</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10700,7 +10705,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10743,7 +10748,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10757,10 +10762,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45224</v>
+        <v>46238</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10773,7 +10778,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10816,7 +10821,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10830,10 +10835,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45244</v>
+        <v>45785</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10846,7 +10851,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10889,7 +10894,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10903,10 +10908,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45377</v>
+        <v>45798</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10919,7 +10924,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10962,7 +10967,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10976,10 +10981,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45218</v>
+        <v>45811</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,13 +10996,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45280</v>
+        <v>45813</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44732</v>
+        <v>45373</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45583</v>
+        <v>45625</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45785</v>
+        <v>45751</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 55708-2023</t>
+          <t>A 37201-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45239</v>
+        <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1410,386 +1410,386 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare
+Slåttergubbe
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 26989-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Nötkråka
+Kungsfågel
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 55708-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Talltita
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 37201-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 15249-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Sexfläckig bastardsvärmare
-Slåttergubbe
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 15249-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Kornknutmossa
 Smal svampklubba
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 26989-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45811</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Nötkråka
-Kungsfågel
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55274-2025</t>
+          <t>A 63592-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45968</v>
+        <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="I13" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1859,460 +1859,460 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Stor revmossa
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9491-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45715</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 55274-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Skuggmossa
 Trådticka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 34938-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44796</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 27676-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>46190</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>3</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 63592-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44508</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 34938-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44796</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9491-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45715</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45239</v>
+        <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2593,53 +2593,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2653,10 +2649,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45587</v>
+        <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2669,17 +2665,17 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2693,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2709,42 +2705,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 21398-2023</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2754,14 +2750,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45063</v>
+        <v>44697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2770,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2818,38 +2814,38 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2863,10 +2859,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46163</v>
+        <v>45813</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2879,17 +2875,17 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.1</v>
+        <v>14.1</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2903,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2919,42 +2915,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2968,10 +2964,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45175</v>
+        <v>45740</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2980,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2993,13 +2989,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3011,7 +3007,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3024,42 +3020,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3073,10 +3069,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44902</v>
+        <v>45239</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,7 +3085,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3122,49 +3118,53 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44697</v>
+        <v>46163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 21398-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45224</v>
+        <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3339,42 +3339,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45813</v>
+        <v>45587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,16 +3404,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>14.1</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3444,42 +3444,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>45224</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3533,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3549,35 +3549,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 71648-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45377</v>
+        <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 71648-2021</t>
+          <t>A 19782-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44543</v>
+        <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19782-2022</t>
+          <t>A 63595-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4470,14 +4470,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44694</v>
+        <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4533,7 +4533,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45393</v>
+        <v>44873</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 51162-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4623,7 +4623,7 @@
         <v>45219</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45219</v>
+        <v>45651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 63595-2021</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44508</v>
+        <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51162-2023</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45219</v>
+        <v>45798</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45281</v>
+        <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4981,14 +4981,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45287</v>
+        <v>45219</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45686</v>
+        <v>45811</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45313</v>
+        <v>45813</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45321</v>
+        <v>45373</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45307</v>
+        <v>45895</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44873</v>
+        <v>45895</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5365,8 +5365,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5409,7 +5414,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5423,10 +5428,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44908</v>
+        <v>45625</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5439,7 +5444,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5482,7 +5487,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5496,10 +5501,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45895</v>
+        <v>45012</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5511,13 +5516,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45895</v>
+        <v>45168</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45167</v>
+        <v>45925</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46098</v>
+        <v>45751</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45705</v>
+        <v>45936</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45012</v>
+        <v>45935</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46107</v>
+        <v>45934</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46107</v>
+        <v>45107</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46107</v>
+        <v>44573</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6154,14 +6154,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46106</v>
+        <v>45686</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45651</v>
+        <v>45950</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45925</v>
+        <v>45002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45560</v>
+        <v>44532</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45935</v>
+        <v>44911</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45936</v>
+        <v>45754</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45934</v>
+        <v>45968</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45950</v>
+        <v>44733</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.1</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45219</v>
+        <v>45994</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45168</v>
+        <v>45107</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44960</v>
+        <v>45704</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45747</v>
+        <v>45715</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46002</v>
+        <v>45715</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45968</v>
+        <v>46098</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44732</v>
+        <v>45705</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44733</v>
+        <v>45587</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46002</v>
+        <v>45336</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7395,14 +7395,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44547</v>
+        <v>46106</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45754</v>
+        <v>46107</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45587</v>
+        <v>46107</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45994</v>
+        <v>44826</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44826</v>
+        <v>46107</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>11.5</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45704</v>
+        <v>45560</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44732</v>
+        <v>45167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45715</v>
+        <v>45167</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45715</v>
+        <v>45747</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45058</v>
+        <v>45608</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46072</v>
+        <v>45587</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44784</v>
+        <v>46002</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45855</v>
+        <v>45393</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45140</v>
+        <v>46002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45336</v>
+        <v>44547</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44532</v>
+        <v>45315</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45280</v>
+        <v>45324</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45587</v>
+        <v>45336</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45315</v>
+        <v>44721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45324</v>
+        <v>45281</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44573</v>
+        <v>45321</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45377</v>
+        <v>45307</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45608</v>
+        <v>44732</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45218</v>
+        <v>44960</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,13 +9093,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9142,7 +9137,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9156,10 +9151,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45629</v>
+        <v>45219</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9172,7 +9167,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9215,7 +9210,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9229,10 +9224,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45244</v>
+        <v>45219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9245,7 +9240,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9288,7 +9283,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9302,10 +9297,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44911</v>
+        <v>45313</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9318,7 +9313,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9361,7 +9356,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9375,10 +9370,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45002</v>
+        <v>46072</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9391,7 +9386,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9434,7 +9429,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9448,10 +9443,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45107</v>
+        <v>45140</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9464,7 +9459,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9507,7 +9502,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9521,10 +9516,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46212</v>
+        <v>44784</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9537,7 +9532,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9580,7 +9575,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9590,14 +9585,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45107</v>
+        <v>45287</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9610,7 +9605,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9653,7 +9648,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9667,10 +9662,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44721</v>
+        <v>45855</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9683,7 +9678,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9726,7 +9721,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9740,10 +9735,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45167</v>
+        <v>44908</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9756,7 +9751,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9799,7 +9794,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9813,10 +9808,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46212</v>
+        <v>45377</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9829,7 +9824,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9872,7 +9867,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9886,10 +9881,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45583</v>
+        <v>45058</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9902,7 +9897,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9945,7 +9940,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9955,14 +9950,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45336</v>
+        <v>45237</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9975,7 +9970,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10018,7 +10013,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10028,14 +10023,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45237</v>
+        <v>45224</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10048,7 +10043,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10091,7 +10086,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10105,10 +10100,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46223</v>
+        <v>45244</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10121,7 +10116,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10164,7 +10159,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10178,10 +10173,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46225</v>
+        <v>45377</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10194,7 +10189,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10237,7 +10232,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10247,14 +10242,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10267,7 +10262,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10310,7 +10305,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10324,10 +10319,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45219</v>
+        <v>45218</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10337,6 +10332,11 @@
       <c r="G122" t="inlineStr">
         <is>
           <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -10383,7 +10383,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46269</v>
+        <v>46212</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46230</v>
+        <v>45280</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45224</v>
+        <v>44732</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10675,7 +10675,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10689,10 +10689,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10758,14 +10758,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45785</v>
+        <v>45583</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10894,7 +10894,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45798</v>
+        <v>46230</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10967,7 +10967,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45811</v>
+        <v>46269</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45813</v>
+        <v>46238</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45373</v>
+        <v>46238</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45625</v>
+        <v>46238</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45751</v>
+        <v>45785</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 26989-2025</t>
+          <t>A 55708-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45811</v>
+        <v>45239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1523,273 +1523,273 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 15249-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Kornknutmossa
+Smal svampklubba
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 26989-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Nötkråka
 Kungsfågel
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 55708-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 15249-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Kornknutmossa
-Smal svampklubba
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 63592-2021</t>
+          <t>A 9491-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44508</v>
+        <v>45715</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1860,42 +1860,42 @@
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
-Vanlig padda</t>
+Revlummer</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 9491-2025</t>
+          <t>A 63592-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45715</v>
+        <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1966,42 +1966,42 @@
       <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
-Revlummer</t>
+Vanlig padda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55274-2025</t>
+          <t>A 27676-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45968</v>
+        <v>46190</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2071,248 +2071,248 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Klippfrullania
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 55274-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Skuggmossa
 Trådticka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 34938-2022</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>44796</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>2.3</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27676-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44902</v>
+        <v>45740</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,23 +2560,23 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
@@ -2584,10 +2584,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2600,42 +2600,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45175</v>
+        <v>45587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2665,16 +2665,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2705,42 +2705,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2750,14 +2750,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44697</v>
+        <v>45239</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2803,49 +2803,53 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2859,10 +2863,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45813</v>
+        <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2875,16 +2879,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>14.1</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2899,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2915,42 +2919,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2964,10 +2968,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45740</v>
+        <v>45175</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2980,7 +2984,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2989,13 +2993,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3007,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3020,42 +3024,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3065,14 +3069,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45239</v>
+        <v>44697</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3085,7 +3089,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3118,53 +3122,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 21398-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46163</v>
+        <v>45063</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21398-2023</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45063</v>
+        <v>44902</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3343,38 +3343,38 @@
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45587</v>
+        <v>45224</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,13 +3404,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3444,42 +3444,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45224</v>
+        <v>45813</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,17 +3509,17 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.4</v>
+        <v>14.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3549,35 +3549,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44873</v>
+        <v>45281</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
         <v>45219</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45651</v>
+        <v>45377</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45629</v>
+        <v>45393</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45798</v>
+        <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4915,7 +4915,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45219</v>
+        <v>45313</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45811</v>
+        <v>44873</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45813</v>
+        <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45373</v>
+        <v>45168</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45895</v>
+        <v>44960</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45895</v>
+        <v>46098</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5365,13 +5365,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5414,7 +5409,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5428,10 +5423,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45625</v>
+        <v>45705</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5444,7 +5439,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5487,7 +5482,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5501,10 +5496,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45012</v>
+        <v>46107</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5517,7 +5512,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5560,7 +5555,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5574,10 +5569,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45168</v>
+        <v>46107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5590,7 +5585,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5633,7 +5628,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5647,10 +5642,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45925</v>
+        <v>46107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5663,7 +5658,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5706,7 +5701,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5716,14 +5711,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45751</v>
+        <v>46106</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5736,7 +5731,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5779,7 +5774,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5793,10 +5788,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45936</v>
+        <v>44732</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5809,7 +5804,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5852,7 +5847,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5866,10 +5861,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45935</v>
+        <v>45751</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,7 +5877,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5925,7 +5920,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5939,10 +5934,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45934</v>
+        <v>44733</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5955,7 +5950,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5998,7 +5993,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6012,10 +6007,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45107</v>
+        <v>45895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,8 +6022,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44573</v>
+        <v>45895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45686</v>
+        <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45950</v>
+        <v>45560</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45002</v>
+        <v>45587</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44532</v>
+        <v>45686</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44911</v>
+        <v>45012</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45754</v>
+        <v>44826</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>11.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45968</v>
+        <v>45747</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44733</v>
+        <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45994</v>
+        <v>45925</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45107</v>
+        <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45704</v>
+        <v>45058</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45715</v>
+        <v>44547</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45715</v>
+        <v>45935</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46098</v>
+        <v>45936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45705</v>
+        <v>45934</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45587</v>
+        <v>45140</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45336</v>
+        <v>46072</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7395,14 +7395,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46106</v>
+        <v>44532</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46107</v>
+        <v>45950</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46107</v>
+        <v>45855</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44826</v>
+        <v>45315</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46107</v>
+        <v>45377</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45560</v>
+        <v>45608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45167</v>
+        <v>45629</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45167</v>
+        <v>45968</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45747</v>
+        <v>45107</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45608</v>
+        <v>44721</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45587</v>
+        <v>45167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46002</v>
+        <v>45583</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8271,14 +8271,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45393</v>
+        <v>45287</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46002</v>
+        <v>46212</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44547</v>
+        <v>46212</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45315</v>
+        <v>45994</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45324</v>
+        <v>45321</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45336</v>
+        <v>45307</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44721</v>
+        <v>46223</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45281</v>
+        <v>46225</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8855,14 +8855,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45321</v>
+        <v>46225</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45307</v>
+        <v>44908</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44732</v>
+        <v>45167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44960</v>
+        <v>46269</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9151,10 +9151,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45219</v>
+        <v>45651</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45219</v>
+        <v>46230</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45313</v>
+        <v>45704</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46072</v>
+        <v>45715</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45140</v>
+        <v>45715</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44784</v>
+        <v>46238</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9585,14 +9585,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45287</v>
+        <v>46238</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9648,7 +9648,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45855</v>
+        <v>46238</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44908</v>
+        <v>44732</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45377</v>
+        <v>44784</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9881,10 +9881,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45058</v>
+        <v>45336</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9940,7 +9940,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9950,14 +9950,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45237</v>
+        <v>45280</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10013,7 +10013,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10027,10 +10027,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45224</v>
+        <v>45587</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10086,7 +10086,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45244</v>
+        <v>45324</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10159,7 +10159,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10173,10 +10173,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45377</v>
+        <v>44573</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46212</v>
+        <v>45218</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,8 +10261,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10305,7 +10310,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10319,10 +10324,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45218</v>
+        <v>45244</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,13 +10339,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46212</v>
+        <v>44911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45280</v>
+        <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44732</v>
+        <v>45107</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46223</v>
+        <v>45336</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10675,7 +10675,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10685,14 +10685,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46225</v>
+        <v>45237</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10758,14 +10758,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46225</v>
+        <v>45219</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45583</v>
+        <v>45224</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10894,7 +10894,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46230</v>
+        <v>45785</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10967,7 +10967,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46269</v>
+        <v>45798</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46238</v>
+        <v>45811</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46238</v>
+        <v>45813</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46238</v>
+        <v>45373</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45785</v>
+        <v>45625</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>46105</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45811</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 9491-2025</t>
+          <t>A 63592-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45715</v>
+        <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1860,42 +1860,42 @@
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
-Revlummer</t>
+Vanlig padda</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 63592-2021</t>
+          <t>A 34938-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44508</v>
+        <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,20 +1925,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.699999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1949,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -1961,47 +1961,47 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Stor revmossa
-Vanlig padda</t>
+          <t>Igelkott
+Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 27676-2026</t>
+          <t>A 55274-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46190</v>
+        <v>45968</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2071,149 +2071,149 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Skuggmossa
+Trådticka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 27676-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Klippfrullania
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 55274-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45968</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmossa
-Trådticka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34938-2022</t>
+          <t>A 9491-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44796</v>
+        <v>45715</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2243,19 +2243,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2267,10 +2267,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
@@ -2279,40 +2279,40 @@
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
+          <t>Stor revmossa
 Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45740</v>
+        <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2584,10 +2584,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2600,42 +2600,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45587</v>
+        <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2665,17 +2665,17 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2705,42 +2705,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2750,14 +2750,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45239</v>
+        <v>44697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2803,53 +2803,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2863,10 +2859,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46163</v>
+        <v>45239</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2879,7 +2875,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2912,49 +2908,53 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45175</v>
+        <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,16 +2984,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3024,42 +3024,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 21398-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3069,14 +3069,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44697</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3133,38 +3133,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21398-2023</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45063</v>
+        <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44902</v>
+        <v>45224</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3339,42 +3339,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45224</v>
+        <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.4</v>
+        <v>14.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3444,42 +3444,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45813</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>14.1</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3518,13 +3518,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3536,7 +3536,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3549,35 +3549,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45281</v>
+        <v>44873</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
         <v>45219</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45377</v>
+        <v>45651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45393</v>
+        <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4842,7 +4842,7 @@
         <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4915,7 +4915,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45313</v>
+        <v>45168</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44873</v>
+        <v>45107</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45219</v>
+        <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45168</v>
+        <v>44532</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44960</v>
+        <v>44911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46098</v>
+        <v>45002</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45705</v>
+        <v>45754</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46107</v>
+        <v>44733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46107</v>
+        <v>45747</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46107</v>
+        <v>46002</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5711,14 +5711,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46106</v>
+        <v>46002</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5774,7 +5774,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44732</v>
+        <v>45895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5847,7 +5847,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45751</v>
+        <v>45895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5876,8 +5876,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5920,7 +5925,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5934,10 +5939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44733</v>
+        <v>45012</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5950,7 +5955,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5993,7 +5998,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6007,10 +6012,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45895</v>
+        <v>44547</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6022,13 +6027,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45895</v>
+        <v>45107</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45754</v>
+        <v>45925</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45560</v>
+        <v>45587</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45587</v>
+        <v>45336</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45686</v>
+        <v>45936</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45012</v>
+        <v>45935</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44826</v>
+        <v>45934</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>11.5</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45747</v>
+        <v>44826</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46002</v>
+        <v>45950</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>6.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45925</v>
+        <v>45167</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46002</v>
+        <v>45167</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45058</v>
+        <v>45968</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44547</v>
+        <v>45608</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45935</v>
+        <v>45587</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45936</v>
+        <v>45393</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45934</v>
+        <v>45315</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45140</v>
+        <v>45324</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46072</v>
+        <v>45336</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44532</v>
+        <v>44721</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45950</v>
+        <v>45994</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45855</v>
+        <v>45281</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45315</v>
+        <v>45321</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45377</v>
+        <v>45704</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45608</v>
+        <v>45715</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45629</v>
+        <v>45715</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45968</v>
+        <v>45307</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45107</v>
+        <v>46072</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44721</v>
+        <v>44732</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45167</v>
+        <v>44960</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45583</v>
+        <v>45219</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8271,14 +8271,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45287</v>
+        <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46212</v>
+        <v>45313</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46212</v>
+        <v>45140</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45994</v>
+        <v>44784</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8563,14 +8563,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45321</v>
+        <v>45287</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45307</v>
+        <v>45855</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46223</v>
+        <v>44908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46225</v>
+        <v>45377</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8855,14 +8855,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46225</v>
+        <v>46098</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44908</v>
+        <v>45705</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9001,14 +9001,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45167</v>
+        <v>46106</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46269</v>
+        <v>46107</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9151,10 +9151,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45651</v>
+        <v>46107</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46230</v>
+        <v>46107</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45704</v>
+        <v>45058</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9366,14 +9366,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45715</v>
+        <v>45237</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45715</v>
+        <v>45224</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46238</v>
+        <v>45560</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46238</v>
+        <v>45244</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9648,7 +9648,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46238</v>
+        <v>45377</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44732</v>
+        <v>45218</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,8 +9750,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9794,7 +9799,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9808,10 +9813,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44784</v>
+        <v>45280</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9867,7 +9872,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9881,10 +9886,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45336</v>
+        <v>44732</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,7 +9902,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9940,7 +9945,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9954,10 +9959,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45280</v>
+        <v>46212</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9970,7 +9975,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10013,7 +10018,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10027,10 +10032,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45587</v>
+        <v>46212</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10043,7 +10048,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10086,7 +10091,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10100,10 +10105,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45324</v>
+        <v>45583</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10116,7 +10121,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10159,7 +10164,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10173,10 +10178,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44573</v>
+        <v>46223</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10189,7 +10194,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10232,7 +10237,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10246,10 +10251,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45218</v>
+        <v>46225</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,13 +10266,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10310,7 +10310,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10320,14 +10320,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45244</v>
+        <v>46225</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44911</v>
+        <v>46230</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45002</v>
+        <v>46269</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45107</v>
+        <v>45785</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45336</v>
+        <v>46238</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10675,7 +10675,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10685,14 +10685,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45237</v>
+        <v>46238</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10762,10 +10762,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45219</v>
+        <v>46238</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45224</v>
+        <v>45798</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10894,7 +10894,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45785</v>
+        <v>45811</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10967,7 +10967,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45798</v>
+        <v>45813</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45811</v>
+        <v>45373</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45813</v>
+        <v>45625</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45373</v>
+        <v>45751</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45625</v>
+        <v>45686</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>46105</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45811</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45968</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>46190</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45715</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45239</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45224</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44873</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>45219</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>45651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45168</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>45107</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44532</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45002</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45754</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45747</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>46002</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>46002</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>45895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45012</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44547</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45107</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45925</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>45587</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>45336</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>45936</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45935</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>45934</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44826</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45950</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45167</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>45167</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45968</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>45608</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45587</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>45393</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>45315</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45324</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>45336</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>44721</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>45994</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45281</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45321</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>45704</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>45715</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>45715</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>45307</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>46072</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44732</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44960</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45219</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45313</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45140</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44784</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45287</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45855</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45377</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>46098</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45705</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>46106</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>46107</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>46107</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>46107</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45058</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45237</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45224</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45560</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45244</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45377</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45218</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>45280</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44732</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>46212</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>46212</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45583</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>46223</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>46225</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>46225</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>46230</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>46269</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>45785</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>46238</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46238</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46238</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45798</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45811</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45813</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45373</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45625</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45751</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45686</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>46105</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45811</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34938-2022</t>
+          <t>A 55274-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44796</v>
+        <v>45968</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,19 +1925,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1949,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -1961,146 +1961,146 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Skuggmossa
+Trådticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 34938-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44796</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 55274-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45968</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmossa
-Trådticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>46190</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45715</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45239</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45224</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44873</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>45219</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>45651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45168</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45107</v>
+        <v>45002</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44573</v>
+        <v>44532</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44532</v>
+        <v>45107</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44911</v>
+        <v>44573</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45002</v>
+        <v>44911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45754</v>
+        <v>45686</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44733</v>
+        <v>45895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45747</v>
+        <v>45895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5584,8 +5584,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5628,7 +5633,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5642,10 +5647,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46002</v>
+        <v>45754</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5658,7 +5663,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5701,7 +5706,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46002</v>
+        <v>45747</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5731,7 +5736,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5774,7 +5779,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5788,10 +5793,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45895</v>
+        <v>46002</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5804,7 +5809,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5847,7 +5852,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5861,10 +5866,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45895</v>
+        <v>44733</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5876,13 +5881,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45012</v>
+        <v>46002</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44547</v>
+        <v>45012</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45107</v>
+        <v>45925</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45925</v>
+        <v>44547</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45587</v>
+        <v>45936</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45336</v>
+        <v>45935</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45936</v>
+        <v>45934</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45935</v>
+        <v>45107</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45934</v>
+        <v>45950</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44826</v>
+        <v>45587</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45950</v>
+        <v>45336</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45167</v>
+        <v>45968</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45167</v>
+        <v>44826</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45968</v>
+        <v>46072</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45608</v>
+        <v>45167</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45587</v>
+        <v>45994</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45393</v>
+        <v>45167</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45315</v>
+        <v>45608</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45324</v>
+        <v>45704</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45336</v>
+        <v>45855</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44721</v>
+        <v>45715</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45994</v>
+        <v>45715</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45281</v>
+        <v>45587</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.1</v>
+        <v>0.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45321</v>
+        <v>45393</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45704</v>
+        <v>45315</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45715</v>
+        <v>45324</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45715</v>
+        <v>45336</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45307</v>
+        <v>44721</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46072</v>
+        <v>45281</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44732</v>
+        <v>45321</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44960</v>
+        <v>45307</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45219</v>
+        <v>44732</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45219</v>
+        <v>44960</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45313</v>
+        <v>46098</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45140</v>
+        <v>45705</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44784</v>
+        <v>45219</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8563,14 +8563,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45287</v>
+        <v>45219</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45855</v>
+        <v>45313</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8709,14 +8709,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44908</v>
+        <v>46106</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45377</v>
+        <v>46107</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46098</v>
+        <v>46107</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45705</v>
+        <v>46107</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9001,14 +9001,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46106</v>
+        <v>45140</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46107</v>
+        <v>45560</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9151,10 +9151,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46107</v>
+        <v>44784</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9220,14 +9220,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46107</v>
+        <v>45287</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45058</v>
+        <v>44908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9366,14 +9366,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45237</v>
+        <v>45377</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45224</v>
+        <v>46212</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45560</v>
+        <v>46212</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45244</v>
+        <v>45058</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9648,7 +9648,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9658,14 +9658,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45377</v>
+        <v>45237</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45218</v>
+        <v>45224</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,13 +9750,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9799,7 +9794,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9813,10 +9808,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45280</v>
+        <v>46223</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9829,7 +9824,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9872,7 +9867,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9886,10 +9881,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44732</v>
+        <v>46225</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9902,7 +9897,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9945,7 +9940,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9955,14 +9950,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9975,7 +9970,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10018,7 +10013,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10032,10 +10027,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46212</v>
+        <v>45244</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10048,7 +10043,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10091,7 +10086,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10105,10 +10100,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45583</v>
+        <v>45377</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10121,7 +10116,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10164,7 +10159,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10178,10 +10173,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46223</v>
+        <v>45218</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10193,8 +10188,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10237,7 +10237,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10310,7 +10310,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10320,14 +10320,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46225</v>
+        <v>46269</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46230</v>
+        <v>45280</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46269</v>
+        <v>44732</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45785</v>
+        <v>46238</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10619,7 +10619,7 @@
         <v>46238</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10675,7 +10675,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10692,7 +10692,7 @@
         <v>46238</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10762,10 +10762,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46238</v>
+        <v>45583</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>6.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45798</v>
+        <v>45785</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10894,7 +10894,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45811</v>
+        <v>45798</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10967,7 +10967,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45813</v>
+        <v>45811</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45373</v>
+        <v>45813</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45625</v>
+        <v>45373</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45751</v>
+        <v>45625</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45686</v>
+        <v>45751</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37201-2023</t>
+          <t>A 55708-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45155</v>
+        <v>45239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1410,379 +1410,379 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 26989-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Nötkråka
+Kungsfågel
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 37201-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Sexfläckig bastardsvärmare
 Slåttergubbe
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 55708-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 15249-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 15249-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Kornknutmossa
 Smal svampklubba
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 26989-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45811</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Nötkråka
-Kungsfågel
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
         <v/>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45968</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34938-2022</t>
+          <t>A 9491-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44796</v>
+        <v>45715</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2031,19 +2031,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2055,10 +2055,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2067,252 +2067,252 @@
         <v>2</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 34938-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44796</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 27676-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>46190</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>3</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9491-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45715</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44902</v>
+        <v>45239</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2593,42 +2593,46 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
@@ -2652,7 +2656,7 @@
         <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2740,7 +2744,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2750,14 +2754,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44697</v>
+        <v>45813</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2770,17 +2774,17 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>14.1</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -2794,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2810,42 +2814,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2859,10 +2863,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45239</v>
+        <v>45587</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2875,7 +2879,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2908,53 +2912,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2964,14 +2964,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46163</v>
+        <v>44697</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3028,38 +3028,38 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21398-2023</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3069,14 +3069,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,23 +3089,23 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3113,10 +3113,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3129,42 +3129,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 21398-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45587</v>
+        <v>45063</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45224</v>
+        <v>44902</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3339,42 +3339,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45813</v>
+        <v>45224</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,16 +3404,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>14.1</v>
+        <v>5.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3444,42 +3444,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>46163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3533,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3549,35 +3549,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 71648-2021</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44543</v>
+        <v>45587</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19782-2022</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44694</v>
+        <v>45785</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44873</v>
+        <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>11.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51162-2023</t>
+          <t>A 71648-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45219</v>
+        <v>44543</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 19782-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4689,14 +4689,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45651</v>
+        <v>44694</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 51162-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45629</v>
+        <v>45219</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45219</v>
+        <v>45281</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45219</v>
+        <v>45377</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45168</v>
+        <v>45686</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45002</v>
+        <v>45393</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44532</v>
+        <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45107</v>
+        <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44573</v>
+        <v>45058</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44911</v>
+        <v>45798</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45686</v>
+        <v>45313</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45895</v>
+        <v>45140</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>45895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45754</v>
+        <v>45895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45747</v>
+        <v>44873</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46002</v>
+        <v>45012</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44733</v>
+        <v>44532</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46002</v>
+        <v>45925</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45012</v>
+        <v>45811</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45925</v>
+        <v>45935</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44547</v>
+        <v>45936</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45936</v>
+        <v>45934</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45935</v>
+        <v>45813</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45934</v>
+        <v>45315</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45107</v>
+        <v>45377</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6526,7 +6526,7 @@
         <v>45950</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45587</v>
+        <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45336</v>
+        <v>45608</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45968</v>
+        <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44826</v>
+        <v>45625</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46072</v>
+        <v>45219</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45167</v>
+        <v>45168</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45994</v>
+        <v>45107</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45167</v>
+        <v>44721</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45608</v>
+        <v>44960</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45704</v>
+        <v>45167</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45855</v>
+        <v>45968</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45715</v>
+        <v>45583</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>6.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45715</v>
+        <v>44732</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45587</v>
+        <v>44733</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45393</v>
+        <v>45754</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45315</v>
+        <v>45994</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7760,14 +7760,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45324</v>
+        <v>45287</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45336</v>
+        <v>45321</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44721</v>
+        <v>45307</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45281</v>
+        <v>45704</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.1</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45321</v>
+        <v>45715</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45307</v>
+        <v>45715</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44732</v>
+        <v>44908</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44960</v>
+        <v>45167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46098</v>
+        <v>45651</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45705</v>
+        <v>46098</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45219</v>
+        <v>45705</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45219</v>
+        <v>44732</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45313</v>
+        <v>46107</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8709,14 +8709,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8789,7 +8789,7 @@
         <v>46107</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8855,14 +8855,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46107</v>
+        <v>44784</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45140</v>
+        <v>45751</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45560</v>
+        <v>45336</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9151,10 +9151,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44784</v>
+        <v>45280</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9220,14 +9220,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45287</v>
+        <v>45560</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44908</v>
+        <v>45587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45377</v>
+        <v>45324</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46212</v>
+        <v>44573</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46212</v>
+        <v>45218</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,8 +9531,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9575,7 +9580,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9589,10 +9594,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45058</v>
+        <v>45244</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9610,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9648,7 +9653,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9658,14 +9663,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45237</v>
+        <v>44911</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9678,7 +9683,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9721,7 +9726,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9735,10 +9740,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45224</v>
+        <v>45002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9751,7 +9756,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9794,7 +9799,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9808,10 +9813,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46223</v>
+        <v>45107</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9824,7 +9829,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9867,7 +9872,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9881,10 +9886,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46225</v>
+        <v>45747</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,7 +9902,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9940,7 +9945,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9950,14 +9955,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46225</v>
+        <v>45336</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9970,7 +9975,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10013,7 +10018,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10023,14 +10028,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45244</v>
+        <v>45237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10043,7 +10048,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10086,7 +10091,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10100,10 +10105,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45377</v>
+        <v>46002</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10116,7 +10121,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10159,7 +10164,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10173,10 +10178,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45218</v>
+        <v>45219</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10186,11 +10191,6 @@
       <c r="G120" t="inlineStr">
         <is>
           <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -10237,7 +10237,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46230</v>
+        <v>46002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10310,7 +10310,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46269</v>
+        <v>44547</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45280</v>
+        <v>45224</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44732</v>
+        <v>46072</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46238</v>
+        <v>45855</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46238</v>
+        <v>46212</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10675,7 +10675,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10689,10 +10689,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46238</v>
+        <v>46212</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10762,10 +10762,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45583</v>
+        <v>46223</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45785</v>
+        <v>46225</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10904,14 +10904,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45798</v>
+        <v>46225</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10967,7 +10967,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45811</v>
+        <v>46269</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45813</v>
+        <v>46230</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45373</v>
+        <v>46238</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45625</v>
+        <v>46238</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45751</v>
+        <v>46238</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 55708-2023</t>
+          <t>A 37201-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45239</v>
+        <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1410,379 +1410,379 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare
+Slåttergubbe
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 55708-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Talltita
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 15249-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Kornknutmossa
+Smal svampklubba
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 26989-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>45811</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>4.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Nötkråka
 Kungsfågel
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 37201-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Sexfläckig bastardsvärmare
-Slåttergubbe
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 15249-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Kornknutmossa
-Smal svampklubba
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
         <v/>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45968</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 9491-2025</t>
+          <t>A 34938-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45715</v>
+        <v>44796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2031,20 +2031,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2055,10 +2055,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2067,252 +2067,252 @@
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 27676-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 9491-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45715</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 34938-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44796</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27676-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45239</v>
+        <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2593,46 +2593,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
@@ -2656,7 +2652,7 @@
         <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2744,7 +2740,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2754,14 +2750,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45813</v>
+        <v>44697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,16 +2770,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>14.1</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2798,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2814,42 +2810,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2863,10 +2859,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45587</v>
+        <v>45239</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2879,7 +2875,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2912,49 +2908,53 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2964,14 +2964,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44697</v>
+        <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3028,38 +3028,38 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 21398-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3069,14 +3069,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45740</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3113,10 +3113,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3129,42 +3129,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21398-2023</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45063</v>
+        <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44902</v>
+        <v>45224</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3339,42 +3339,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45224</v>
+        <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.4</v>
+        <v>14.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3444,42 +3444,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46163</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,23 +3509,23 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
@@ -3533,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3549,35 +3549,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 71648-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45587</v>
+        <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 19782-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45785</v>
+        <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44826</v>
+        <v>44873</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 71648-2021</t>
+          <t>A 51162-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44543</v>
+        <v>45219</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19782-2022</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4689,14 +4689,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44694</v>
+        <v>45651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51162-2023</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45219</v>
+        <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45281</v>
+        <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45377</v>
+        <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45686</v>
+        <v>45168</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45393</v>
+        <v>45107</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45219</v>
+        <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45219</v>
+        <v>45002</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45058</v>
+        <v>44532</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45798</v>
+        <v>44911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45313</v>
+        <v>45686</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45140</v>
+        <v>45895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>45895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45895</v>
+        <v>45754</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44873</v>
+        <v>44733</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5796,7 +5796,7 @@
         <v>45012</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44532</v>
+        <v>45747</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45925</v>
+        <v>46002</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45811</v>
+        <v>45925</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45935</v>
+        <v>46002</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>45936</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45813</v>
+        <v>45934</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45315</v>
+        <v>45107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45377</v>
+        <v>45950</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45950</v>
+        <v>45587</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45373</v>
+        <v>45336</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45608</v>
+        <v>44547</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45629</v>
+        <v>44826</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>11.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45625</v>
+        <v>45968</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45219</v>
+        <v>45167</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45168</v>
+        <v>45994</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45107</v>
+        <v>45167</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44721</v>
+        <v>45608</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44960</v>
+        <v>45587</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45167</v>
+        <v>45393</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45968</v>
+        <v>45704</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45583</v>
+        <v>45715</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44732</v>
+        <v>45715</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44733</v>
+        <v>45315</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45754</v>
+        <v>45324</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45994</v>
+        <v>45336</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7760,14 +7760,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45287</v>
+        <v>44721</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45321</v>
+        <v>45281</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45307</v>
+        <v>45321</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45704</v>
+        <v>46072</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45715</v>
+        <v>45307</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45715</v>
+        <v>44732</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44908</v>
+        <v>44960</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45167</v>
+        <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45651</v>
+        <v>45219</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46098</v>
+        <v>45313</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45705</v>
+        <v>46098</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44732</v>
+        <v>45705</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46107</v>
+        <v>45855</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8709,14 +8709,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8789,7 +8789,7 @@
         <v>46107</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8855,14 +8855,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44784</v>
+        <v>46107</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45751</v>
+        <v>45140</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45336</v>
+        <v>44784</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9147,14 +9147,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45280</v>
+        <v>45287</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9227,7 +9227,7 @@
         <v>45560</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45587</v>
+        <v>44908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45324</v>
+        <v>45377</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44573</v>
+        <v>45058</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9512,14 +9512,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45218</v>
+        <v>45237</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,13 +9531,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9580,7 +9575,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9594,10 +9589,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45244</v>
+        <v>45224</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9610,7 +9605,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9653,7 +9648,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9667,10 +9662,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44911</v>
+        <v>46212</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9683,7 +9678,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9726,7 +9721,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9740,10 +9735,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45002</v>
+        <v>46212</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9756,7 +9751,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9799,7 +9794,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9813,10 +9808,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45107</v>
+        <v>45244</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9829,7 +9824,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9872,7 +9867,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9886,10 +9881,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45747</v>
+        <v>45377</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9902,7 +9897,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9945,7 +9940,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9959,10 +9954,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45336</v>
+        <v>45218</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9974,8 +9969,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10018,7 +10018,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10028,14 +10028,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45237</v>
+        <v>45280</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10091,7 +10091,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10105,10 +10105,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46002</v>
+        <v>44732</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10164,7 +10164,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10178,10 +10178,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45219</v>
+        <v>46223</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10237,7 +10237,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>46225</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10310,7 +10310,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10320,14 +10320,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44547</v>
+        <v>46225</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45224</v>
+        <v>46230</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46072</v>
+        <v>46269</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45855</v>
+        <v>45583</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46212</v>
+        <v>46238</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10675,7 +10675,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10689,10 +10689,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46212</v>
+        <v>46238</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10762,10 +10762,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46225</v>
+        <v>45785</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10904,14 +10904,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46225</v>
+        <v>45798</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10967,7 +10967,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46269</v>
+        <v>45811</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46230</v>
+        <v>45813</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46238</v>
+        <v>45373</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46238</v>
+        <v>45625</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46238</v>
+        <v>45751</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37201-2023</t>
+          <t>A 55708-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45155</v>
+        <v>45239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1410,168 +1410,168 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37201-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sexfläckig bastardsvärmare
 Slåttergubbe
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 55708-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15249-2026</t>
+          <t>A 26989-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46105</v>
+        <v>45811</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1640,156 +1640,156 @@
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Nötkråka
+Kungsfågel
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 15249-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Kornknutmossa
 Smal svampklubba
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 26989-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45811</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Nötkråka
-Kungsfågel
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 63592-2021</t>
+          <t>A 55274-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44508</v>
+        <v>45968</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1859,460 +1859,460 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Skuggmossa
+Trådticka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9491-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45715</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 63592-2021</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44508</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Stor revmossa
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 55274-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45968</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 27676-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 34938-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44796</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmossa
-Trådticka</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 34938-2022</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44796</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 27676-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9491-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45715</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44902</v>
+        <v>45239</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2593,49 +2593,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2649,10 +2653,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45175</v>
+        <v>45587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2665,16 +2669,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2689,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2705,42 +2709,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2750,14 +2754,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44697</v>
+        <v>45813</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2770,17 +2774,17 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>14.1</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -2794,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2810,42 +2814,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2859,10 +2863,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45239</v>
+        <v>45740</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2875,23 +2879,23 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
@@ -2899,55 +2903,51 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
         <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21398-2023</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3069,14 +3069,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>45175</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,17 +3089,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3129,42 +3129,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45587</v>
+        <v>44697</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 21398-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45224</v>
+        <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3339,42 +3339,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45813</v>
+        <v>44902</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,16 +3404,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>14.1</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3444,42 +3444,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>45224</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3533,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3549,35 +3549,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44873</v>
+        <v>45281</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51162-2023</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45219</v>
+        <v>45377</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 51162-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45651</v>
+        <v>45219</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45629</v>
+        <v>45393</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4842,7 +4842,7 @@
         <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4915,7 +4915,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45168</v>
+        <v>45313</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45107</v>
+        <v>45686</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44573</v>
+        <v>45715</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45002</v>
+        <v>44873</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44532</v>
+        <v>45798</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44911</v>
+        <v>45895</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5365,8 +5365,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5409,7 +5414,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5423,10 +5428,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45686</v>
+        <v>45895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5439,7 +5444,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5482,7 +5487,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5496,10 +5501,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45895</v>
+        <v>45012</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5512,7 +5517,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5555,7 +5560,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5569,10 +5574,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45895</v>
+        <v>45925</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5584,13 +5589,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45754</v>
+        <v>45935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44733</v>
+        <v>45936</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45012</v>
+        <v>45934</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45747</v>
+        <v>46098</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46002</v>
+        <v>45705</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45925</v>
+        <v>45811</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46002</v>
+        <v>45950</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>6.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45936</v>
+        <v>45219</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45935</v>
+        <v>45168</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45934</v>
+        <v>46107</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45107</v>
+        <v>46107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45950</v>
+        <v>46107</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45587</v>
+        <v>44960</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6592,14 +6592,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45336</v>
+        <v>46106</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44547</v>
+        <v>45968</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44826</v>
+        <v>44732</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>11.5</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45968</v>
+        <v>45560</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45167</v>
+        <v>45813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45994</v>
+        <v>45373</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45167</v>
+        <v>44733</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45608</v>
+        <v>45754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7183,7 +7183,7 @@
         <v>45587</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45393</v>
+        <v>45625</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45704</v>
+        <v>45994</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45715</v>
+        <v>45747</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45715</v>
+        <v>44826</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>11.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45315</v>
+        <v>46002</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45324</v>
+        <v>45704</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45336</v>
+        <v>45715</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44721</v>
+        <v>46002</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45281</v>
+        <v>44547</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7.1</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45321</v>
+        <v>45058</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46072</v>
+        <v>45140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45307</v>
+        <v>46072</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44732</v>
+        <v>45751</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44960</v>
+        <v>44532</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45219</v>
+        <v>45855</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45219</v>
+        <v>45315</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45313</v>
+        <v>45377</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46098</v>
+        <v>45608</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45705</v>
+        <v>45629</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45855</v>
+        <v>45107</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8709,14 +8709,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46106</v>
+        <v>44721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46107</v>
+        <v>45167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46107</v>
+        <v>46212</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46107</v>
+        <v>45583</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45140</v>
+        <v>46212</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44784</v>
+        <v>45287</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9147,14 +9147,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45287</v>
+        <v>46223</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45560</v>
+        <v>46225</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9293,14 +9293,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44908</v>
+        <v>46225</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45377</v>
+        <v>45321</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45058</v>
+        <v>45307</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9512,14 +9512,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45237</v>
+        <v>46269</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45224</v>
+        <v>46230</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9648,7 +9648,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46212</v>
+        <v>44908</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46212</v>
+        <v>45167</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45244</v>
+        <v>45651</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9881,10 +9881,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45377</v>
+        <v>46238</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9940,7 +9940,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45218</v>
+        <v>46238</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,13 +9969,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10018,7 +10013,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10032,10 +10027,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45280</v>
+        <v>46238</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10048,7 +10043,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10108,7 +10103,7 @@
         <v>44732</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10164,7 +10159,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10178,10 +10173,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46223</v>
+        <v>44784</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10194,7 +10189,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10237,7 +10232,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10251,10 +10246,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46225</v>
+        <v>45336</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10267,7 +10262,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10310,7 +10305,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10320,14 +10315,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46225</v>
+        <v>45280</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10340,7 +10335,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10383,7 +10378,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10397,10 +10392,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46230</v>
+        <v>45587</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10413,7 +10408,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10456,7 +10451,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10470,10 +10465,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46269</v>
+        <v>45324</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10486,7 +10481,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10529,7 +10524,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10543,10 +10538,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45583</v>
+        <v>44573</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10559,7 +10554,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10602,7 +10597,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10616,10 +10611,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46238</v>
+        <v>45218</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10631,8 +10626,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10675,7 +10675,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10689,10 +10689,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46238</v>
+        <v>45244</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10762,10 +10762,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46238</v>
+        <v>44911</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45785</v>
+        <v>45002</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10894,7 +10894,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45798</v>
+        <v>45107</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10967,7 +10967,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45811</v>
+        <v>45336</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11050,14 +11050,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45813</v>
+        <v>45237</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45373</v>
+        <v>45219</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45625</v>
+        <v>45224</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45751</v>
+        <v>45785</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45811</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>46105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>45968</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>44508</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>46190</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>44796</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45239</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>45587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45813</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>45740</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45175</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>44697</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>44902</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>45224</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45281</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>45377</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>45219</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45393</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45313</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>45686</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>45715</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44873</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45798</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45895</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>45895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45012</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45925</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45936</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45934</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>46098</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45705</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>45811</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45950</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45219</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>45168</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46107</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>46107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>46107</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44960</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>46106</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45968</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44732</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>45560</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>45373</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44733</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>45754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>45587</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45625</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>45994</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45747</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44826</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>46002</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45704</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>45715</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>46002</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44547</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>45058</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>45140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>46072</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>45751</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44532</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45855</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45315</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45377</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45608</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45629</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45107</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>46212</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45583</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>46212</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45287</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>46223</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>46225</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>46225</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45321</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45307</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>46269</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>46230</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44908</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45167</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45651</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>46238</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>46238</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>46238</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>44732</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44784</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45336</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45280</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45587</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45324</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44573</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45218</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45244</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44911</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45002</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45107</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45336</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45237</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45219</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45224</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45785</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45811</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>46105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>45968</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>44508</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>46190</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>44796</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45239</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>45587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45813</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>45740</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45175</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>44697</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>44902</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>45224</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45281</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>45377</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>45219</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45393</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45313</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>45686</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>45715</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44873</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45798</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45895</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>45895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45012</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45925</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45936</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45934</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>46098</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45705</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>45811</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45950</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45219</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>45168</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46107</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>46107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>46107</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44960</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>46106</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45968</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44732</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>45560</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>45373</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44733</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>45754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>45587</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45625</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>45994</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45747</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44826</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>46002</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45704</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>45715</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>46002</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44547</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>45058</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>45140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>46072</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>45751</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44532</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45855</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45315</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45377</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45608</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45629</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45107</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>46212</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45583</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>46212</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45287</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>46223</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>46225</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>46225</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45321</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45307</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>46269</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>46230</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44908</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45167</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45651</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>46238</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>46238</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>46238</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>44732</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44784</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45336</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45280</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45587</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45324</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44573</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45218</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45244</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44911</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45002</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45107</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45336</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45237</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45219</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45224</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45785</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 55708-2023</t>
+          <t>A 37201-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45239</v>
+        <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1410,272 +1410,272 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare
+Slåttergubbe
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 26989-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Nötkråka
+Kungsfågel
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 55708-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Talltita
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 37201-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Sexfläckig bastardsvärmare
-Slåttergubbe
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 26989-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45811</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Nötkråka
-Kungsfågel
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
         <v/>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
         <v>46105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55274-2025</t>
+          <t>A 63592-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45968</v>
+        <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="I13" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1859,255 +1859,255 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Stor revmossa
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9491-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45715</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 55274-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Skuggmossa
 Trådticka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9491-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45715</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 63592-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44508</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 27676-2026</t>
+          <t>A 34938-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46190</v>
+        <v>44796</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2137,20 +2137,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2173,146 +2173,146 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27676-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 34938-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44796</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45239</v>
+        <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2593,53 +2593,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2653,10 +2649,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45587</v>
+        <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2669,17 +2665,17 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2693,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2709,42 +2705,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2754,14 +2750,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45813</v>
+        <v>44697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,16 +2770,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>14.1</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2798,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2814,42 +2810,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2863,10 +2859,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45740</v>
+        <v>45813</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2879,7 +2875,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>14.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2888,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2906,7 +2902,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2919,42 +2915,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2968,10 +2964,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46163</v>
+        <v>45239</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2980,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3017,49 +3013,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45175</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3098,13 +3098,13 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3116,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3129,42 +3129,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44697</v>
+        <v>46163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3238,31 +3238,31 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
         <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44902</v>
+        <v>45587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3448,31 +3448,31 @@
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
         <v>45224</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44494</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44615</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44784</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44543</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44694</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45281</v>
+        <v>44873</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 51162-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45377</v>
+        <v>45219</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51162-2023</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45219</v>
+        <v>45785</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45393</v>
+        <v>45651</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45219</v>
+        <v>45798</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45219</v>
+        <v>45895</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45313</v>
+        <v>45895</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5000,8 +5000,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5044,7 +5049,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5058,10 +5063,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45686</v>
+        <v>45629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5074,7 +5079,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5117,7 +5122,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5131,10 +5136,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45715</v>
+        <v>45811</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5147,7 +5152,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5190,7 +5195,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5204,10 +5209,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44873</v>
+        <v>45012</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5220,7 +5225,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5263,7 +5268,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5277,10 +5282,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45798</v>
+        <v>45813</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5293,7 +5298,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5336,7 +5341,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5350,10 +5355,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45895</v>
+        <v>45219</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5365,13 +5370,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45895</v>
+        <v>45219</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5487,7 +5487,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45012</v>
+        <v>45373</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45925</v>
+        <v>45625</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45935</v>
+        <v>45704</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45936</v>
+        <v>45925</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45934</v>
+        <v>45715</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46098</v>
+        <v>45715</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45705</v>
+        <v>45936</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45811</v>
+        <v>45935</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45950</v>
+        <v>45934</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45219</v>
+        <v>45168</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45168</v>
+        <v>45950</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46107</v>
+        <v>45751</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46107</v>
+        <v>45686</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46107</v>
+        <v>45968</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44960</v>
+        <v>45107</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6592,14 +6592,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46106</v>
+        <v>44573</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45968</v>
+        <v>45002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44732</v>
+        <v>44532</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45560</v>
+        <v>44911</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45813</v>
+        <v>45994</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45373</v>
+        <v>45754</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7037,7 +7037,7 @@
         <v>44733</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45754</v>
+        <v>45107</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45587</v>
+        <v>46098</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45625</v>
+        <v>45705</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45994</v>
+        <v>45587</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7395,14 +7395,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45747</v>
+        <v>46106</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44826</v>
+        <v>46107</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11.5</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46002</v>
+        <v>46107</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45704</v>
+        <v>46107</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45715</v>
+        <v>45336</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46002</v>
+        <v>44826</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>11.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44547</v>
+        <v>45560</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45058</v>
+        <v>45167</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45140</v>
+        <v>45747</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46072</v>
+        <v>45167</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45751</v>
+        <v>46002</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44532</v>
+        <v>45608</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45855</v>
+        <v>46002</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45315</v>
+        <v>45587</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45377</v>
+        <v>45393</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45608</v>
+        <v>44547</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45629</v>
+        <v>45315</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45107</v>
+        <v>45324</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44721</v>
+        <v>45336</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45167</v>
+        <v>44721</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46212</v>
+        <v>45281</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>7.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45583</v>
+        <v>45321</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46212</v>
+        <v>45307</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45287</v>
+        <v>44732</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9151,10 +9151,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46223</v>
+        <v>44960</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46225</v>
+        <v>45219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9293,14 +9293,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46225</v>
+        <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45321</v>
+        <v>45313</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45307</v>
+        <v>46072</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46269</v>
+        <v>45140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46230</v>
+        <v>44784</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9648,7 +9648,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9658,14 +9658,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44908</v>
+        <v>45287</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45167</v>
+        <v>45855</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45651</v>
+        <v>44908</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9881,10 +9881,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46238</v>
+        <v>45377</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9940,7 +9940,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46238</v>
+        <v>45058</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10013,7 +10013,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10023,14 +10023,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46238</v>
+        <v>45237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10086,7 +10086,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44732</v>
+        <v>45224</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10159,7 +10159,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10173,10 +10173,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44784</v>
+        <v>45244</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45336</v>
+        <v>45377</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10305,7 +10305,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45280</v>
+        <v>46212</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10378,7 +10378,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45587</v>
+        <v>45218</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,8 +10407,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10451,7 +10456,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10465,10 +10470,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45324</v>
+        <v>46212</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10481,7 +10486,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10524,7 +10529,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10538,10 +10543,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44573</v>
+        <v>45280</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10554,7 +10559,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10597,7 +10602,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10611,10 +10616,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45218</v>
+        <v>44732</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,13 +10631,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10675,7 +10675,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10689,10 +10689,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45244</v>
+        <v>46223</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10762,10 +10762,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44911</v>
+        <v>46225</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10831,14 +10831,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45002</v>
+        <v>46225</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10894,7 +10894,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45107</v>
+        <v>45583</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10967,7 +10967,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45336</v>
+        <v>46230</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11050,14 +11050,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45237</v>
+        <v>46269</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45219</v>
+        <v>46238</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45224</v>
+        <v>46238</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45785</v>
+        <v>46238</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE135"/>
+  <dimension ref="A1:AE134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37201-2023</t>
+          <t>A 26989-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45155</v>
+        <v>45811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1407,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1422,260 +1422,260 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Nötkråka
+Kungsfågel
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 55708-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 37201-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Sexfläckig bastardsvärmare
 Slåttergubbe
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 26989-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45811</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Nötkråka
-Kungsfågel
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 55708-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
         <v/>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
         <v>46105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 63592-2021</t>
+          <t>A 9491-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44508</v>
+        <v>45715</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1860,42 +1860,42 @@
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
-Vanlig padda</t>
+Revlummer</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 9491-2025</t>
+          <t>A 55274-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45715</v>
+        <v>45968</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1965,43 +1965,43 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Stor revmossa
-Revlummer</t>
+          <t>Skuggmossa
+Trådticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55274-2025</t>
+          <t>A 63592-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45968</v>
+        <v>44508</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="I15" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2071,43 +2071,43 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skuggmossa
-Trådticka</t>
+          <t>Stor revmossa
+Vanlig padda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34938-2022</t>
+          <t>A 27676-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44796</v>
+        <v>46190</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2137,19 +2137,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2173,146 +2173,146 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 34938-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44796</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27676-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44902</v>
+        <v>45239</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2593,49 +2593,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2649,10 +2653,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45175</v>
+        <v>45813</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2665,7 +2669,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>14.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2705,42 +2709,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2750,14 +2754,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44697</v>
+        <v>45740</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2770,23 +2774,23 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -2794,10 +2798,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2810,42 +2814,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2859,10 +2863,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45813</v>
+        <v>45587</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2875,16 +2879,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>14.1</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2899,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2915,42 +2919,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2964,10 +2968,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45239</v>
+        <v>45175</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2980,17 +2984,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3004,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3013,53 +3017,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3069,14 +3069,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45740</v>
+        <v>44697</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3113,10 +3113,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3129,35 +3129,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
         <v>46163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45587</v>
+        <v>44902</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3448,31 +3448,31 @@
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
         <v>45224</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25504-2022</t>
+          <t>A 40282-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44732</v>
+        <v>46294</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3614,13 +3614,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3644,20 +3644,52 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 40282-2026 artfynd.xlsx", "A 40282-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 40282-2026 karta.png", "A 40282-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 40282-2026 georefererad karta.tif", "A 40282-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 40282-2026 FSC-klagomål.docx", "A 40282-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 40282-2026 FSC-klagomål mail.docx", "A 40282-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 40282-2026 tillsynsbegäran.docx", "A 40282-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 40282-2026 tillsynsbegäran mail.docx", "A 40282-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6111-2022</t>
+          <t>A 25504-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3667,14 +3699,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44599</v>
+        <v>44732</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3687,7 +3719,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3730,7 +3762,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10460-2022</t>
+          <t>A 6111-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3740,14 +3772,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44623</v>
+        <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3760,7 +3792,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3803,7 +3835,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53200-2021</t>
+          <t>A 10460-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3817,10 +3849,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44468</v>
+        <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3833,7 +3865,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3893,7 +3925,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3966,7 +3998,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4022,7 +4054,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 53204-2021</t>
+          <t>A 59767-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4036,10 +4068,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44468</v>
+        <v>44494</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4052,7 +4084,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4095,7 +4127,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59767-2021</t>
+          <t>A 9165-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4109,10 +4141,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44494</v>
+        <v>44615</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4125,7 +4157,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4168,7 +4200,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9165-2022</t>
+          <t>A 32869-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4182,10 +4214,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44615</v>
+        <v>44784</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4198,7 +4230,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4241,7 +4273,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32869-2022</t>
+          <t>A 71648-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4255,10 +4287,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44784</v>
+        <v>44543</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4271,7 +4303,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4314,7 +4346,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 71648-2021</t>
+          <t>A 19782-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4324,14 +4356,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44543</v>
+        <v>44694</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4387,7 +4419,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19782-2022</t>
+          <t>A 63595-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4397,14 +4429,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44694</v>
+        <v>44508</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4417,7 +4449,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4460,7 +4492,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63595-2021</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4474,10 +4506,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44508</v>
+        <v>45281</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4490,7 +4522,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4533,7 +4565,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4547,10 +4579,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44873</v>
+        <v>45377</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4563,7 +4595,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4606,7 +4638,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51162-2023</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4620,10 +4652,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45219</v>
+        <v>45393</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4636,7 +4668,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4679,7 +4711,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4693,10 +4725,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45785</v>
+        <v>45219</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4709,7 +4741,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4752,7 +4784,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4766,10 +4798,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45651</v>
+        <v>45219</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4782,7 +4814,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4825,7 +4857,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 51162-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4839,10 +4871,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45798</v>
+        <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4855,7 +4887,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4898,7 +4930,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4912,10 +4944,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45895</v>
+        <v>45313</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4928,7 +4960,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +5003,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4985,10 +5017,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45895</v>
+        <v>45686</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5000,13 +5032,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5049,7 +5076,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5063,10 +5090,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45629</v>
+        <v>45715</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5079,7 +5106,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5122,7 +5149,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5136,10 +5163,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45811</v>
+        <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5152,7 +5179,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5195,7 +5222,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5209,10 +5236,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45012</v>
+        <v>45798</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5225,7 +5252,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5268,7 +5295,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5282,10 +5309,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45813</v>
+        <v>45895</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,8 +5324,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5341,7 +5373,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5355,10 +5387,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45219</v>
+        <v>45895</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5371,7 +5403,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5414,7 +5446,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5428,10 +5460,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45219</v>
+        <v>45012</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5444,7 +5476,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5487,7 +5519,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5501,10 +5533,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45373</v>
+        <v>45811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5517,7 +5549,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5560,7 +5592,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5574,10 +5606,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45625</v>
+        <v>45813</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5590,7 +5622,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5633,7 +5665,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5647,10 +5679,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45704</v>
+        <v>45373</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5663,7 +5695,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5706,7 +5738,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5720,10 +5752,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45925</v>
+        <v>45625</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5736,7 +5768,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5779,7 +5811,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5793,10 +5825,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45715</v>
+        <v>45925</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5852,7 +5884,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5866,10 +5898,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45715</v>
+        <v>45935</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,7 +5914,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5942,7 +5974,7 @@
         <v>45936</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5998,7 +6030,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6012,10 +6044,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45935</v>
+        <v>45934</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6028,7 +6060,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6071,7 +6103,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6085,10 +6117,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45934</v>
+        <v>45751</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,7 +6133,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6144,7 +6176,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6158,10 +6190,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45168</v>
+        <v>45950</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,7 +6206,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6249,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6263,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45950</v>
+        <v>45219</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6279,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6322,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6336,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45751</v>
+        <v>45168</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,7 +6352,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6363,7 +6395,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6409,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45686</v>
+        <v>44960</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6425,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6453,7 +6485,7 @@
         <v>45968</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6509,7 +6541,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6523,10 +6555,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45107</v>
+        <v>44732</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6539,7 +6571,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6582,7 +6614,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6596,10 +6628,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44573</v>
+        <v>44733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,7 +6644,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6655,7 +6687,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6669,10 +6701,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45002</v>
+        <v>45754</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6685,7 +6717,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6728,7 +6760,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6742,10 +6774,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44532</v>
+        <v>45587</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6758,7 +6790,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6801,7 +6833,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6815,10 +6847,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44911</v>
+        <v>45994</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6831,7 +6863,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6874,7 +6906,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6888,10 +6920,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45994</v>
+        <v>44826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6904,7 +6936,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6947,7 +6979,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6961,10 +6993,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45754</v>
+        <v>46098</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6977,7 +7009,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7020,7 +7052,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7034,10 +7066,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44733</v>
+        <v>45704</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,7 +7082,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7093,7 +7125,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7107,10 +7139,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45107</v>
+        <v>45715</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7123,7 +7155,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7166,7 +7198,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7212,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46098</v>
+        <v>45705</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7228,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7271,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7285,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45705</v>
+        <v>46107</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7269,7 +7301,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7312,7 +7344,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7358,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45587</v>
+        <v>46107</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7374,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7417,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7395,14 +7427,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7415,7 +7447,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7458,7 +7490,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7468,14 +7500,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7488,7 +7520,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7531,7 +7563,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7545,10 +7577,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46107</v>
+        <v>45058</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7593,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7604,7 +7636,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7650,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46107</v>
+        <v>45560</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7634,7 +7666,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7677,7 +7709,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7723,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45336</v>
+        <v>45140</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7739,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7782,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7764,10 +7796,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44826</v>
+        <v>45747</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7812,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7855,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7869,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45560</v>
+        <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7885,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7928,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7942,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45167</v>
+        <v>44532</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7926,7 +7958,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7969,7 +8001,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7983,10 +8015,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45747</v>
+        <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7999,7 +8031,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8042,7 +8074,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8056,10 +8088,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45167</v>
+        <v>44547</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8072,7 +8104,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8115,7 +8147,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8129,10 +8161,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46002</v>
+        <v>45315</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8145,7 +8177,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8188,7 +8220,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8202,10 +8234,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45608</v>
+        <v>45377</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8218,7 +8250,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8261,7 +8293,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8275,10 +8307,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46002</v>
+        <v>45608</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8291,7 +8323,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8334,7 +8366,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8348,10 +8380,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45587</v>
+        <v>45629</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8364,7 +8396,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8407,7 +8439,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8421,10 +8453,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45393</v>
+        <v>45107</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8437,7 +8469,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8480,7 +8512,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8494,10 +8526,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44547</v>
+        <v>44721</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8510,7 +8542,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8553,7 +8585,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8567,10 +8599,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45315</v>
+        <v>45167</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8583,7 +8615,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8626,7 +8658,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8640,10 +8672,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45324</v>
+        <v>45583</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8656,7 +8688,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8699,7 +8731,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8713,10 +8745,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45336</v>
+        <v>46072</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8729,7 +8761,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8772,7 +8804,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8782,14 +8814,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44721</v>
+        <v>45287</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8802,7 +8834,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8845,7 +8877,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8859,10 +8891,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45281</v>
+        <v>45855</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8875,7 +8907,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8935,7 +8967,7 @@
         <v>45321</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9008,7 +9040,7 @@
         <v>45307</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9064,7 +9096,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9078,10 +9110,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44732</v>
+        <v>44908</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9137,7 +9169,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9151,10 +9183,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44960</v>
+        <v>45167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9167,7 +9199,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9210,7 +9242,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9224,10 +9256,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45219</v>
+        <v>45651</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9272,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9283,7 +9315,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9297,10 +9329,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45219</v>
+        <v>46212</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9345,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9356,7 +9388,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9370,10 +9402,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45313</v>
+        <v>44732</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9418,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9429,7 +9461,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9443,10 +9475,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46072</v>
+        <v>46212</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9491,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9502,7 +9534,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9516,10 +9548,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45140</v>
+        <v>44784</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9532,7 +9564,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9575,7 +9607,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9589,10 +9621,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44784</v>
+        <v>45336</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9637,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9648,7 +9680,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9658,14 +9690,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45287</v>
+        <v>45280</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9678,7 +9710,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9721,7 +9753,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9735,10 +9767,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45855</v>
+        <v>46223</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9751,7 +9783,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9794,7 +9826,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9808,10 +9840,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44908</v>
+        <v>46225</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9824,7 +9856,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9867,7 +9899,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9877,14 +9909,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45377</v>
+        <v>46225</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,7 +9929,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9940,7 +9972,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9954,10 +9986,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45058</v>
+        <v>45587</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9970,7 +10002,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10013,7 +10045,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10023,14 +10055,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45237</v>
+        <v>46269</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10043,7 +10075,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10086,7 +10118,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10100,10 +10132,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45224</v>
+        <v>46230</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10116,7 +10148,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10159,7 +10191,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10173,10 +10205,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45244</v>
+        <v>45324</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10189,7 +10221,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10232,7 +10264,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10246,10 +10278,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45377</v>
+        <v>44573</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10262,7 +10294,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10305,7 +10337,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10319,10 +10351,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46212</v>
+        <v>45218</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,8 +10366,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10378,7 +10415,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10392,10 +10429,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45218</v>
+        <v>45244</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,13 +10444,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10456,7 +10488,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10470,10 +10502,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46212</v>
+        <v>44911</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10486,7 +10518,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10529,7 +10561,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10543,10 +10575,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45280</v>
+        <v>45002</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10559,7 +10591,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10602,7 +10634,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10616,10 +10648,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44732</v>
+        <v>45107</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10632,7 +10664,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10675,7 +10707,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10689,10 +10721,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46223</v>
+        <v>45336</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10705,7 +10737,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10748,7 +10780,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10758,14 +10790,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46225</v>
+        <v>45237</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10778,7 +10810,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10821,7 +10853,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10831,14 +10863,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10851,7 +10883,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10894,7 +10926,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10908,10 +10940,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45583</v>
+        <v>46238</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10924,7 +10956,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10967,7 +10999,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10981,10 +11013,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46230</v>
+        <v>46238</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10997,7 +11029,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11040,7 +11072,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11054,10 +11086,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46269</v>
+        <v>45219</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11070,7 +11102,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11113,7 +11145,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11127,10 +11159,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46238</v>
+        <v>45224</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11143,7 +11175,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11183,10 +11215,10 @@
       </c>
       <c r="V133" s="2" t="inlineStr"/>
     </row>
-    <row r="134" ht="15" customHeight="1">
+    <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11200,10 +11232,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46238</v>
+        <v>45785</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,7 +11248,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11255,79 +11287,6 @@
         <v>0</v>
       </c>
       <c r="V134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>A 32378-2026</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E135" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I135" t="n">
-        <v>1</v>
-      </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE134"/>
+  <dimension ref="A1:AE135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 43202-2024</t>
+          <t>A 16723-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45567</v>
+        <v>45030</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -870,12 +870,124 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Blåmossa
+Kornknutmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 16723-2023 artfynd.xlsx", "A 16723-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 16723-2023 karta.png", "A 16723-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 16723-2023 georefererad karta.tif", "A 16723-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 16723-2023 FSC-klagomål.docx", "A 16723-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 16723-2023 FSC-klagomål mail.docx", "A 16723-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 16723-2023 tillsynsbegäran.docx", "A 16723-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 16723-2023 tillsynsbegäran mail.docx", "A 16723-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 16723-2023 prioriterade fågelarter.docx", "A 16723-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 43202-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45567</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Havstulpanlav
 Rostfläck
@@ -883,144 +995,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 43202-2024 artfynd.xlsx", "A 43202-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 43202-2024 karta.png", "A 43202-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 43202-2024 georefererad karta.tif", "A 43202-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 43202-2024 FSC-klagomål.docx", "A 43202-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 43202-2024 FSC-klagomål mail.docx", "A 43202-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 43202-2024 tillsynsbegäran.docx", "A 43202-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 43202-2024 tillsynsbegäran mail.docx", "A 43202-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 16723-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45030</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Blåmossa
-Kornknutmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 16723-2023 artfynd.xlsx", "A 16723-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 16723-2023 karta.png", "A 16723-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 16723-2023 georefererad karta.tif", "A 16723-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 16723-2023 FSC-klagomål.docx", "A 16723-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 16723-2023 FSC-klagomål mail.docx", "A 16723-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 16723-2023 tillsynsbegäran.docx", "A 16723-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 16723-2023 tillsynsbegäran mail.docx", "A 16723-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 16723-2023 prioriterade fågelarter.docx", "A 16723-2023")</f>
         <v/>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26989-2025</t>
+          <t>A 37201-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45811</v>
+        <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1407,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1422,260 +1422,260 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare
+Slåttergubbe
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 26989-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Nötkråka
 Kungsfågel
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 55708-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45239</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>5.4</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Talltita
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 37201-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Sexfläckig bastardsvärmare
-Slåttergubbe
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
         <v>46105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 9491-2025</t>
+          <t>A 63592-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45715</v>
+        <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1860,42 +1860,42 @@
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
-Revlummer</t>
+Vanlig padda</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55274-2025</t>
+          <t>A 34938-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45968</v>
+        <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,19 +1925,19 @@
         </is>
       </c>
       <c r="I14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1949,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -1961,358 +1961,358 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9491-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45715</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 55274-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Skuggmossa
 Trådticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 63592-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44508</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J15" t="n">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27676-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 27676-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 34938-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44796</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45239</v>
+        <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2593,53 +2593,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2653,10 +2649,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45813</v>
+        <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2669,7 +2665,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>14.1</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2709,42 +2705,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 21398-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2754,14 +2750,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45740</v>
+        <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,10 +2770,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2789,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2798,10 +2794,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2814,42 +2810,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2859,14 +2855,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45587</v>
+        <v>44697</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2879,7 +2875,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2923,38 +2919,38 @@
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2968,10 +2964,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45175</v>
+        <v>45587</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,16 +2980,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3008,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3024,42 +3020,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3069,14 +3065,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44697</v>
+        <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,17 +3085,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>14.1</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3113,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3129,42 +3125,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3178,10 +3174,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46163</v>
+        <v>45224</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,13 +3190,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3234,42 +3230,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21398-2023</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3279,14 +3275,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45063</v>
+        <v>45740</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,23 +3295,23 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
@@ -3323,10 +3319,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3339,42 +3335,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3384,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44902</v>
+        <v>45239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,7 +3400,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3437,49 +3433,53 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45224</v>
+        <v>46163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3549,35 +3549,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         <v>46294</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44732</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 58926-2021</t>
+          <t>A 32869-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44489</v>
+        <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59767-2021</t>
+          <t>A 58926-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44494</v>
+        <v>44489</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4144,7 +4144,7 @@
         <v>44615</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32869-2022</t>
+          <t>A 59767-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44784</v>
+        <v>44494</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4290,7 +4290,7 @@
         <v>44543</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>44694</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 63595-2021</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44508</v>
+        <v>44873</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45281</v>
+        <v>45336</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 63595-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45377</v>
+        <v>44508</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45393</v>
+        <v>44721</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45219</v>
+        <v>45281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45219</v>
+        <v>45321</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51162-2023</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45219</v>
+        <v>44732</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45313</v>
+        <v>45107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45686</v>
+        <v>44573</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45715</v>
+        <v>45002</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44873</v>
+        <v>44532</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45798</v>
+        <v>45307</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45895</v>
+        <v>44911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5324,13 +5324,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5373,7 +5368,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5387,10 +5382,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45895</v>
+        <v>44732</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5403,7 +5398,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5446,7 +5441,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5460,10 +5455,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45012</v>
+        <v>45583</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5476,7 +5471,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5519,7 +5514,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5533,10 +5528,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45811</v>
+        <v>44960</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5549,7 +5544,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5592,7 +5587,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 51162-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5606,10 +5601,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45813</v>
+        <v>45219</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5622,7 +5617,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5665,7 +5660,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5679,10 +5674,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45373</v>
+        <v>45754</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5695,7 +5690,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5738,7 +5733,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5752,10 +5747,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45625</v>
+        <v>45219</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5768,7 +5763,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5811,7 +5806,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5825,10 +5820,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45925</v>
+        <v>45219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5841,7 +5836,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5884,7 +5879,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5898,10 +5893,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45935</v>
+        <v>44733</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5914,7 +5909,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5957,7 +5952,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5971,10 +5966,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45936</v>
+        <v>45313</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5987,7 +5982,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6030,7 +6025,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6044,10 +6039,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45934</v>
+        <v>45140</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6060,7 +6055,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6103,7 +6098,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6117,10 +6112,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45751</v>
+        <v>44784</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6133,7 +6128,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6176,7 +6171,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6186,14 +6181,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45950</v>
+        <v>45287</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6206,7 +6201,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.1</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6249,7 +6244,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6263,10 +6258,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45219</v>
+        <v>44908</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6279,7 +6274,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6322,7 +6317,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6336,10 +6331,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45168</v>
+        <v>45107</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6352,7 +6347,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6395,7 +6390,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6409,10 +6404,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44960</v>
+        <v>45651</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6425,7 +6420,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6468,7 +6463,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6482,10 +6477,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45968</v>
+        <v>45785</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6498,7 +6493,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6541,7 +6536,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6555,10 +6550,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44732</v>
+        <v>45587</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6571,7 +6566,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6614,7 +6609,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6628,10 +6623,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44733</v>
+        <v>45377</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6644,7 +6639,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6687,7 +6682,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6701,10 +6696,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45754</v>
+        <v>45336</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6760,7 +6755,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6774,10 +6769,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45587</v>
+        <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6790,7 +6785,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6833,7 +6828,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6847,10 +6842,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45994</v>
+        <v>44826</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6863,7 +6858,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6906,7 +6901,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6920,10 +6915,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44826</v>
+        <v>45798</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6936,7 +6931,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>11.5</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6979,7 +6974,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6993,10 +6988,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46098</v>
+        <v>45219</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7009,7 +7004,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7052,7 +7047,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7066,10 +7061,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45704</v>
+        <v>45219</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7082,7 +7077,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7125,7 +7120,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7139,10 +7134,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45715</v>
+        <v>45058</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7155,7 +7150,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7198,7 +7193,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7208,14 +7203,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45705</v>
+        <v>45237</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7228,7 +7223,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7271,7 +7266,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7285,10 +7280,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46107</v>
+        <v>45811</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7301,7 +7296,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7344,7 +7339,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7358,10 +7353,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46107</v>
+        <v>45167</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7374,7 +7369,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7417,7 +7412,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7431,10 +7426,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46107</v>
+        <v>45813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7447,7 +7442,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7490,7 +7485,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7500,14 +7495,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46106</v>
+        <v>45224</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7563,7 +7558,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7577,10 +7572,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45058</v>
+        <v>45373</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7593,7 +7588,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7636,7 +7631,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7650,10 +7645,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45560</v>
+        <v>45625</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7666,7 +7661,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7709,7 +7704,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7723,10 +7718,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45140</v>
+        <v>45244</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7739,7 +7734,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7782,7 +7777,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7796,10 +7791,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45747</v>
+        <v>45377</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7812,7 +7807,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7855,7 +7850,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7869,10 +7864,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46002</v>
+        <v>45167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7885,7 +7880,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7928,7 +7923,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7942,10 +7937,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44532</v>
+        <v>45218</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7957,8 +7952,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46002</v>
+        <v>45608</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8074,7 +8074,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8088,10 +8088,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44547</v>
+        <v>45587</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8147,7 +8147,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8161,10 +8161,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45315</v>
+        <v>45393</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8220,7 +8220,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8234,10 +8234,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45377</v>
+        <v>45280</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8293,7 +8293,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8307,10 +8307,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45608</v>
+        <v>45751</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8366,7 +8366,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8380,10 +8380,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45629</v>
+        <v>45315</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8439,7 +8439,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8453,10 +8453,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45107</v>
+        <v>45324</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8512,7 +8512,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44721</v>
+        <v>45168</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45167</v>
+        <v>45936</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8658,7 +8658,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45583</v>
+        <v>45935</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8731,7 +8731,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46072</v>
+        <v>45934</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8804,7 +8804,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8814,14 +8814,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45287</v>
+        <v>45686</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8877,7 +8877,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45855</v>
+        <v>45895</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8950,7 +8950,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45321</v>
+        <v>45895</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8979,8 +8979,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9023,7 +9028,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9037,10 +9042,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45307</v>
+        <v>45950</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9053,7 +9058,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9096,7 +9101,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9110,10 +9115,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44908</v>
+        <v>45012</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9126,7 +9131,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9169,7 +9174,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9183,10 +9188,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45167</v>
+        <v>45968</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9199,7 +9204,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9242,7 +9247,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9256,10 +9261,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45651</v>
+        <v>45925</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9272,7 +9277,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9315,7 +9320,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9329,10 +9334,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46212</v>
+        <v>45994</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9345,7 +9350,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9388,7 +9393,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9402,10 +9407,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44732</v>
+        <v>45704</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9418,7 +9423,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9461,7 +9466,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9475,10 +9480,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46212</v>
+        <v>45715</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9491,7 +9496,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9534,7 +9539,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9548,10 +9553,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44784</v>
+        <v>45715</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9564,7 +9569,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9607,7 +9612,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9621,10 +9626,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45336</v>
+        <v>46098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9680,7 +9685,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9694,10 +9699,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45280</v>
+        <v>45705</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9710,7 +9715,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9753,7 +9758,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9763,14 +9768,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46223</v>
+        <v>46106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9783,7 +9788,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9826,7 +9831,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9840,10 +9845,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46225</v>
+        <v>46107</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9856,7 +9861,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9899,7 +9904,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9909,14 +9914,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46225</v>
+        <v>46107</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9929,7 +9934,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9972,7 +9977,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9986,10 +9991,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45587</v>
+        <v>46107</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10002,7 +10007,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10045,7 +10050,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10059,10 +10064,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46269</v>
+        <v>45560</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10075,7 +10080,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10118,7 +10123,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10132,10 +10137,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46230</v>
+        <v>45747</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10148,7 +10153,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10191,7 +10196,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10205,10 +10210,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45324</v>
+        <v>46002</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10264,7 +10269,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10278,10 +10283,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44573</v>
+        <v>46002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10294,7 +10299,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10337,7 +10342,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10351,10 +10356,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45218</v>
+        <v>44547</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10366,13 +10371,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10415,7 +10415,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10429,10 +10429,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45244</v>
+        <v>46072</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10488,7 +10488,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44911</v>
+        <v>45855</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10561,7 +10561,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10575,10 +10575,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45002</v>
+        <v>46212</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45107</v>
+        <v>46212</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10707,7 +10707,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45336</v>
+        <v>46223</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10790,14 +10790,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45237</v>
+        <v>46225</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10853,7 +10853,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10863,14 +10863,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10926,7 +10926,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46238</v>
+        <v>46230</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10999,7 +10999,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11013,10 +11013,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46238</v>
+        <v>46269</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11072,7 +11072,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11086,10 +11086,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45219</v>
+        <v>46238</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11145,7 +11145,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11159,134 +11159,207 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45224</v>
+        <v>46238</v>
       </c>
       <c r="E133" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134" ht="15" customHeight="1">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>A 32378-2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E134" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>A 40559-2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="n">
         <v>46295</v>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I133" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>A 22271-2025</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="n">
-        <v>45785</v>
-      </c>
-      <c r="E134" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I134" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" s="2" t="inlineStr"/>
+      <c r="E135" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE135"/>
+  <dimension ref="A1:AE136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 16723-2023</t>
+          <t>A 43202-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45030</v>
+        <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -870,12 +870,120 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Havstulpanlav
+Rostfläck
+Stor revmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 43202-2024 artfynd.xlsx", "A 43202-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 43202-2024 karta.png", "A 43202-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 43202-2024 georefererad karta.tif", "A 43202-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 43202-2024 FSC-klagomål.docx", "A 43202-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 43202-2024 FSC-klagomål mail.docx", "A 43202-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 43202-2024 tillsynsbegäran.docx", "A 43202-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 43202-2024 tillsynsbegäran mail.docx", "A 43202-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 16723-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45030</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="U4" t="n">
+      <c r="T5" t="n">
         <v>4</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Blåmossa
@@ -883,144 +991,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 16723-2023 artfynd.xlsx", "A 16723-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 16723-2023 karta.png", "A 16723-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 16723-2023 georefererad karta.tif", "A 16723-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 16723-2023 FSC-klagomål.docx", "A 16723-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 16723-2023 FSC-klagomål mail.docx", "A 16723-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 16723-2023 tillsynsbegäran.docx", "A 16723-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 16723-2023 tillsynsbegäran mail.docx", "A 16723-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 16723-2023 prioriterade fågelarter.docx", "A 16723-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 43202-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45567</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Havstulpanlav
-Rostfläck
-Stor revmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 43202-2024 artfynd.xlsx", "A 43202-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 43202-2024 karta.png", "A 43202-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 43202-2024 georefererad karta.tif", "A 43202-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 43202-2024 FSC-klagomål.docx", "A 43202-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 43202-2024 FSC-klagomål mail.docx", "A 43202-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 43202-2024 tillsynsbegäran.docx", "A 43202-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 43202-2024 tillsynsbegäran mail.docx", "A 43202-2024")</f>
         <v/>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37201-2023</t>
+          <t>A 55708-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45155</v>
+        <v>45239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1410,272 +1410,272 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37201-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sexfläckig bastardsvärmare
 Slåttergubbe
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 26989-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45811</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>4.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Nötkråka
 Kungsfågel
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 55708-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
         <v/>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
         <v>46105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 63592-2021</t>
+          <t>A 55274-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44508</v>
+        <v>45968</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1859,460 +1859,460 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Skuggmossa
+Trådticka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9491-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45715</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 63592-2021</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44508</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Stor revmossa
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 27676-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 34938-2022</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>44796</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>2.3</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9491-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45715</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 55274-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45968</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmossa
-Trådticka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27676-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44902</v>
+        <v>45239</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2593,49 +2593,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2649,10 +2653,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45175</v>
+        <v>45587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2665,16 +2669,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2689,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2705,42 +2709,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 21398-2023</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2750,14 +2754,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45063</v>
+        <v>45813</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2770,17 +2774,17 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>14.1</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -2794,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2810,42 +2814,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2855,14 +2859,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44697</v>
+        <v>45740</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2875,23 +2879,23 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
@@ -2899,10 +2903,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2915,42 +2919,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2964,10 +2968,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45587</v>
+        <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2980,7 +2984,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3024,38 +3028,38 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3069,10 +3073,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45813</v>
+        <v>45175</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3085,7 +3089,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>14.1</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3125,42 +3129,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3170,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45224</v>
+        <v>44697</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3190,13 +3194,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3230,42 +3234,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 21398-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3275,14 +3279,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45740</v>
+        <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3295,10 +3299,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3310,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3319,10 +3323,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3335,42 +3339,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 21398-2023 artfynd.xlsx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 21398-2023 karta.png", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 21398-2023 georefererad karta.tif", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 21398-2023 FSC-klagomål.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 21398-2023 FSC-klagomål mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 21398-2023 tillsynsbegäran.docx", "A 21398-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 21398-2023 tillsynsbegäran mail.docx", "A 21398-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 40282-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3384,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45239</v>
+        <v>46294</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3400,13 +3404,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3436,50 +3440,46 @@
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 40282-2026 artfynd.xlsx", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 40282-2026 karta.png", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 40282-2026 georefererad karta.tif", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 40282-2026 FSC-klagomål.docx", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 40282-2026 FSC-klagomål mail.docx", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 40282-2026 tillsynsbegäran.docx", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 40282-2026 tillsynsbegäran mail.docx", "A 40282-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46163</v>
+        <v>44902</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3553,38 +3553,38 @@
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 40282-2026</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46294</v>
+        <v>45224</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3647,42 +3647,42 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 40282-2026 artfynd.xlsx", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 40282-2026 karta.png", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 40282-2026 georefererad karta.tif", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 40282-2026 FSC-klagomål.docx", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 40282-2026 FSC-klagomål mail.docx", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 40282-2026 tillsynsbegäran.docx", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 40282-2026 tillsynsbegäran mail.docx", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
         <v>44732</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32869-2022</t>
+          <t>A 58926-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44784</v>
+        <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58926-2021</t>
+          <t>A 59767-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44489</v>
+        <v>44494</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4144,7 +4144,7 @@
         <v>44615</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59767-2021</t>
+          <t>A 32869-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44494</v>
+        <v>44784</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4290,7 +4290,7 @@
         <v>44543</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>44694</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 63595-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44873</v>
+        <v>44508</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45336</v>
+        <v>45281</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 63595-2021</t>
+          <t>A 51162-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44508</v>
+        <v>45219</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44721</v>
+        <v>45377</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45281</v>
+        <v>45393</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45321</v>
+        <v>45219</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44732</v>
+        <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45107</v>
+        <v>45313</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44573</v>
+        <v>45686</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45002</v>
+        <v>45715</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44532</v>
+        <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45307</v>
+        <v>45895</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5251,8 +5251,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5295,7 +5300,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5309,10 +5314,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44911</v>
+        <v>45895</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5325,7 +5330,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5368,7 +5373,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 14468-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5382,10 +5387,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44732</v>
+        <v>45012</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5398,7 +5403,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5441,7 +5446,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 24542-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5455,10 +5460,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45583</v>
+        <v>45798</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5471,7 +5476,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5514,7 +5519,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 46349-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5528,10 +5533,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44960</v>
+        <v>45925</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5544,7 +5549,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5587,7 +5592,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 51162-2023</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5601,10 +5606,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45219</v>
+        <v>45935</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5617,7 +5622,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5660,7 +5665,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16679-2025</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5674,10 +5679,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45754</v>
+        <v>45936</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5733,7 +5738,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 48432-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5747,10 +5752,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45219</v>
+        <v>45934</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5763,7 +5768,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5806,7 +5811,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5820,10 +5825,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45219</v>
+        <v>45950</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5836,7 +5841,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>6.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5879,7 +5884,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5893,10 +5898,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44733</v>
+        <v>46098</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5909,7 +5914,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5952,7 +5957,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5966,10 +5971,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45313</v>
+        <v>45705</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5982,7 +5987,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6025,7 +6030,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6039,10 +6044,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45140</v>
+        <v>45811</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6055,7 +6060,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6098,7 +6103,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6112,10 +6117,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44784</v>
+        <v>46107</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6128,7 +6133,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6171,7 +6176,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6181,14 +6186,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45287</v>
+        <v>46107</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6201,7 +6206,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6244,7 +6249,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6258,10 +6263,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44908</v>
+        <v>46107</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6274,7 +6279,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6317,7 +6322,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6327,14 +6332,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45107</v>
+        <v>46106</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6347,7 +6352,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6390,7 +6395,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6404,10 +6409,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45651</v>
+        <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6420,7 +6425,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6463,7 +6468,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6477,10 +6482,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45785</v>
+        <v>45168</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6493,7 +6498,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6536,7 +6541,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6550,10 +6555,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45587</v>
+        <v>45968</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6566,7 +6571,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6609,7 +6614,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6623,10 +6628,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45377</v>
+        <v>45813</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6639,7 +6644,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6682,7 +6687,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6696,10 +6701,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45336</v>
+        <v>44960</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6712,7 +6717,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6755,7 +6760,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6769,10 +6774,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45629</v>
+        <v>45373</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6785,7 +6790,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6828,7 +6833,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6842,10 +6847,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44826</v>
+        <v>45560</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6858,7 +6863,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>11.5</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6901,7 +6906,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24542-2025</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6915,10 +6920,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45798</v>
+        <v>45625</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6931,7 +6936,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6974,7 +6979,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6988,10 +6993,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45219</v>
+        <v>44732</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7004,7 +7009,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7047,7 +7052,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7061,10 +7066,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45219</v>
+        <v>44733</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7077,7 +7082,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7120,7 +7125,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 16679-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7134,10 +7139,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45058</v>
+        <v>45754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7150,7 +7155,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7193,7 +7198,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7203,14 +7208,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45237</v>
+        <v>45994</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7223,7 +7228,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7266,7 +7271,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7280,10 +7285,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45811</v>
+        <v>45587</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7296,7 +7301,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7339,7 +7344,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7353,10 +7358,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45167</v>
+        <v>45747</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7369,7 +7374,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7412,7 +7417,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7426,10 +7431,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45813</v>
+        <v>46002</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7442,7 +7447,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7485,7 +7490,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7499,10 +7504,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45224</v>
+        <v>44826</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7515,7 +7520,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>11.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7558,7 +7563,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7572,10 +7577,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45373</v>
+        <v>45704</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7588,7 +7593,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7631,7 +7636,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7645,10 +7650,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45625</v>
+        <v>45715</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7661,7 +7666,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7704,7 +7709,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7718,10 +7723,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45244</v>
+        <v>45751</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7734,7 +7739,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7777,7 +7782,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7791,10 +7796,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45377</v>
+        <v>46002</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7807,7 +7812,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7850,7 +7855,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7864,10 +7869,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45167</v>
+        <v>44547</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7880,7 +7885,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7923,7 +7928,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7937,10 +7942,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45218</v>
+        <v>45058</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7952,13 +7957,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45608</v>
+        <v>45140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8074,7 +8074,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8088,10 +8088,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45587</v>
+        <v>44532</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8147,7 +8147,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8161,10 +8161,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45393</v>
+        <v>46072</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8234,10 +8234,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45280</v>
+        <v>45855</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8293,7 +8293,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8307,10 +8307,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45751</v>
+        <v>45315</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8366,7 +8366,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8380,10 +8380,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45315</v>
+        <v>45377</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8439,7 +8439,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8453,10 +8453,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45324</v>
+        <v>45608</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8512,7 +8512,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45168</v>
+        <v>45629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45936</v>
+        <v>45107</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8658,7 +8658,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45935</v>
+        <v>44721</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8731,7 +8731,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48432-2025</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45934</v>
+        <v>45167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8804,7 +8804,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45686</v>
+        <v>45583</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.3</v>
+        <v>6.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8877,7 +8877,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45895</v>
+        <v>46212</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8950,7 +8950,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45895</v>
+        <v>46212</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8979,13 +8979,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9028,7 +9023,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9038,14 +9033,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45950</v>
+        <v>45287</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9058,7 +9053,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.1</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9101,7 +9096,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 14468-2023</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9115,10 +9110,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45012</v>
+        <v>45321</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9131,7 +9126,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9174,7 +9169,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9188,10 +9183,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45968</v>
+        <v>45307</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9204,7 +9199,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9247,7 +9242,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 46349-2025</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9261,10 +9256,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45925</v>
+        <v>46223</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9277,7 +9272,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9320,7 +9315,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9334,10 +9329,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45994</v>
+        <v>46225</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9350,7 +9345,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9393,7 +9388,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9403,14 +9398,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45704</v>
+        <v>46225</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9423,7 +9418,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9466,7 +9461,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9480,10 +9475,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45715</v>
+        <v>44908</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9496,7 +9491,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9539,7 +9534,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9553,10 +9548,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45715</v>
+        <v>45167</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9569,7 +9564,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9612,7 +9607,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9626,10 +9621,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46098</v>
+        <v>46269</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9642,7 +9637,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9685,7 +9680,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9699,10 +9694,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45705</v>
+        <v>45651</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9715,7 +9710,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9758,7 +9753,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9768,14 +9763,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46106</v>
+        <v>46230</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9788,7 +9783,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9831,7 +9826,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9845,10 +9840,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46107</v>
+        <v>46238</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9861,7 +9856,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9904,7 +9899,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9918,10 +9913,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46107</v>
+        <v>46238</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9934,7 +9929,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9977,7 +9972,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9991,10 +9986,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46107</v>
+        <v>46238</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10007,7 +10002,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10050,7 +10045,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10064,10 +10059,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45560</v>
+        <v>44732</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10080,7 +10075,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10123,7 +10118,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10137,10 +10132,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45747</v>
+        <v>44784</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10153,7 +10148,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.6</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10196,7 +10191,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10210,10 +10205,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46002</v>
+        <v>45336</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10226,7 +10221,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10269,7 +10264,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10283,10 +10278,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>45280</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10299,7 +10294,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10342,7 +10337,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10356,10 +10351,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44547</v>
+        <v>45587</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10372,7 +10367,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10415,7 +10410,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10429,10 +10424,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46072</v>
+        <v>45324</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10445,7 +10440,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10488,7 +10483,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10502,10 +10497,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45855</v>
+        <v>44573</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10518,7 +10513,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10561,7 +10556,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10575,10 +10570,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46212</v>
+        <v>45218</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10590,8 +10585,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46212</v>
+        <v>45244</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10707,7 +10707,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46223</v>
+        <v>44911</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10794,10 +10794,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46225</v>
+        <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10853,7 +10853,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10863,14 +10863,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46225</v>
+        <v>45107</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10926,7 +10926,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 40751-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46230</v>
+        <v>46296</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10999,7 +10999,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11013,10 +11013,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46269</v>
+        <v>45336</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11072,7 +11072,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11082,14 +11082,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46238</v>
+        <v>45237</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11145,7 +11145,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 40559-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11159,10 +11159,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46238</v>
+        <v>46295</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11218,7 +11218,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11232,10 +11232,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46238</v>
+        <v>45219</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11288,10 +11288,10 @@
       </c>
       <c r="V134" s="2" t="inlineStr"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 40559-2026</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11305,10 +11305,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46295</v>
+        <v>45224</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11360,6 +11360,79 @@
         <v>0</v>
       </c>
       <c r="V135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>A 22271-2025</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>45785</v>
+      </c>
+      <c r="E136" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 55708-2023</t>
+          <t>A 37201-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45239</v>
+        <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1410,161 +1410,161 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare
+Slåttergubbe
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 55708-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Talltita
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 37201-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Sexfläckig bastardsvärmare
-Slåttergubbe
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
         <v>45811</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>46105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55274-2025</t>
+          <t>A 63592-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45968</v>
+        <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="I13" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1859,255 +1859,255 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Stor revmossa
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 55274-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Skuggmossa
 Trådticka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 9491-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>45715</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>1.5</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 63592-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44508</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 63592-2021 artfynd.xlsx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 63592-2021 karta.png", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 63592-2021 georefererad karta.tif", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 63592-2021 FSC-klagomål.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 63592-2021 FSC-klagomål mail.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 63592-2021 tillsynsbegäran.docx", "A 63592-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 63592-2021 tillsynsbegäran mail.docx", "A 63592-2021")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 27676-2026</t>
+          <t>A 34938-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46190</v>
+        <v>44796</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2137,20 +2137,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2173,146 +2173,146 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27676-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27676-2026 artfynd.xlsx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27676-2026 karta.png", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27676-2026 georefererad karta.tif", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27676-2026 FSC-klagomål.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27676-2026 FSC-klagomål mail.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27676-2026 tillsynsbegäran.docx", "A 27676-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27676-2026 tillsynsbegäran mail.docx", "A 27676-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 34938-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44796</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 34938-2022 artfynd.xlsx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 34938-2022 karta.png", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 34938-2022 georefererad karta.tif", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 34938-2022 FSC-klagomål.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 34938-2022 FSC-klagomål mail.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 34938-2022 tillsynsbegäran.docx", "A 34938-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 34938-2022 tillsynsbegäran mail.docx", "A 34938-2022")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55686-2023</t>
+          <t>A 58481-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45239</v>
+        <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2593,53 +2593,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47362-2024</t>
+          <t>A 41457-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2653,10 +2649,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45587</v>
+        <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2669,17 +2665,17 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2693,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2709,42 +2705,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27482-2025</t>
+          <t>A 19977-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2754,14 +2750,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45813</v>
+        <v>44697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,16 +2770,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>14.1</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2798,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2814,42 +2810,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14259-2025</t>
+          <t>A 55686-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2863,10 +2859,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45740</v>
+        <v>45239</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2879,10 +2875,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2894,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2903,58 +2899,62 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55686-2023 artfynd.xlsx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55686-2023 karta.png", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55686-2023 georefererad karta.tif", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55686-2023 FSC-klagomål.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55686-2023 FSC-klagomål mail.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55686-2023 tillsynsbegäran.docx", "A 55686-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55686-2023 tillsynsbegäran mail.docx", "A 55686-2023")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55686-2023 prioriterade fågelarter.docx", "A 55686-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23492-2026</t>
+          <t>A 27482-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46163</v>
+        <v>45813</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,17 +2984,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>14.1</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3024,42 +3024,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 27482-2025 artfynd.xlsx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 27482-2025 karta.png", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 27482-2025 georefererad karta.tif", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 27482-2025 FSC-klagomål.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 27482-2025 FSC-klagomål mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 27482-2025 tillsynsbegäran.docx", "A 27482-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 27482-2025 tillsynsbegäran mail.docx", "A 27482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41457-2023</t>
+          <t>A 14259-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45175</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3098,13 +3098,13 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3116,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3129,42 +3129,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 41457-2023 artfynd.xlsx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 14259-2025 artfynd.xlsx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 41457-2023 karta.png", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 14259-2025 karta.png", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 41457-2023 georefererad karta.tif", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 14259-2025 georefererad karta.tif", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 41457-2023 FSC-klagomål.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 14259-2025 FSC-klagomål.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 41457-2023 FSC-klagomål mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 14259-2025 FSC-klagomål mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 41457-2023 tillsynsbegäran.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 14259-2025 tillsynsbegäran.docx", "A 14259-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 41457-2023 tillsynsbegäran mail.docx", "A 41457-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 14259-2025 tillsynsbegäran mail.docx", "A 14259-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 19977-2022</t>
+          <t>A 23492-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,14 +3174,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44697</v>
+        <v>46163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3238,31 +3238,31 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 19977-2022 artfynd.xlsx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 23492-2026 artfynd.xlsx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 19977-2022 karta.png", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 23492-2026 karta.png", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 19977-2022 georefererad karta.tif", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 23492-2026 georefererad karta.tif", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 19977-2022 FSC-klagomål.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 23492-2026 FSC-klagomål.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 19977-2022 FSC-klagomål mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 23492-2026 FSC-klagomål mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 19977-2022 tillsynsbegäran.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 23492-2026 tillsynsbegäran.docx", "A 23492-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 19977-2022 tillsynsbegäran mail.docx", "A 19977-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 23492-2026 tillsynsbegäran mail.docx", "A 23492-2026")</f>
         <v/>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
         <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 40282-2026</t>
+          <t>A 47362-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46294</v>
+        <v>45587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3404,13 +3404,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3437,49 +3437,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 40282-2026 artfynd.xlsx", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 47362-2024 artfynd.xlsx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 40282-2026 karta.png", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 47362-2024 karta.png", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 40282-2026 georefererad karta.tif", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 47362-2024 georefererad karta.tif", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 40282-2026 FSC-klagomål.docx", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 47362-2024 FSC-klagomål.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 40282-2026 FSC-klagomål mail.docx", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 47362-2024 FSC-klagomål mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 40282-2026 tillsynsbegäran.docx", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 47362-2024 tillsynsbegäran.docx", "A 47362-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 40282-2026 tillsynsbegäran mail.docx", "A 40282-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 47362-2024 tillsynsbegäran mail.docx", "A 47362-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58481-2022</t>
+          <t>A 52164-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44902</v>
+        <v>45224</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3549,42 +3549,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 58481-2022 artfynd.xlsx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 58481-2022 karta.png", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 58481-2022 georefererad karta.tif", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 58481-2022 FSC-klagomål.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 58481-2022 FSC-klagomål mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 58481-2022 tillsynsbegäran.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 58481-2022 tillsynsbegäran mail.docx", "A 58481-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52164-2023</t>
+          <t>A 40282-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45224</v>
+        <v>46294</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3647,42 +3647,42 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 52164-2023 artfynd.xlsx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 40282-2026 artfynd.xlsx", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 52164-2023 karta.png", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 40282-2026 karta.png", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 52164-2023 georefererad karta.tif", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 40282-2026 georefererad karta.tif", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 52164-2023 FSC-klagomål.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 40282-2026 FSC-klagomål.docx", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 52164-2023 FSC-klagomål mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 40282-2026 FSC-klagomål mail.docx", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 52164-2023 tillsynsbegäran.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 40282-2026 tillsynsbegäran.docx", "A 40282-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 52164-2023 tillsynsbegäran mail.docx", "A 52164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 40282-2026 tillsynsbegäran mail.docx", "A 40282-2026")</f>
         <v/>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
         <v>44732</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44494</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44615</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>44784</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44543</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>44694</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44508</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64560-2023</t>
+          <t>A 52045-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45281</v>
+        <v>44873</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4582,7 +4582,7 @@
         <v>45219</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12091-2024</t>
+          <t>A 22271-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45377</v>
+        <v>45785</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14183-2024</t>
+          <t>A 61874-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45393</v>
+        <v>45651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51127-2023</t>
+          <t>A 7356-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45219</v>
+        <v>45704</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51130-2023</t>
+          <t>A 9492-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45219</v>
+        <v>45715</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2605-2024</t>
+          <t>A 9494-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45313</v>
+        <v>45715</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4433-2025</t>
+          <t>A 40306-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45686</v>
+        <v>45895</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9494-2025</t>
+          <t>A 40273-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45715</v>
+        <v>45895</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5105,8 +5105,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5149,7 +5154,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52045-2022</t>
+          <t>A 57269-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5163,10 +5168,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44873</v>
+        <v>45629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5179,7 +5184,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5222,7 +5227,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 40273-2025</t>
+          <t>A 51154-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5236,10 +5241,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45895</v>
+        <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5251,13 +5256,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5300,7 +5300,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40306-2025</t>
+          <t>A 51157-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45895</v>
+        <v>45219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
         <v>45012</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45798</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45925</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48440-2025</t>
+          <t>A 48538-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5606,10 +5606,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45935</v>
+        <v>45936</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5665,7 +5665,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48538-2025</t>
+          <t>A 48440-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45936</v>
+        <v>45935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5755,7 +5755,7 @@
         <v>45934</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51501-2025</t>
+          <t>A 40053-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45950</v>
+        <v>45168</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5884,7 +5884,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13951-2026</t>
+          <t>A 26992-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46098</v>
+        <v>45811</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5957,7 +5957,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7575-2025</t>
+          <t>A 51501-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5971,10 +5971,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45705</v>
+        <v>45950</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26992-2025</t>
+          <t>A 27513-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6044,10 +6044,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45811</v>
+        <v>45813</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6103,7 +6103,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15698-2026</t>
+          <t>A 11697-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6117,10 +6117,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46107</v>
+        <v>45373</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6176,7 +6176,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15700-2026</t>
+          <t>A 13951-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46107</v>
+        <v>46098</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15704-2026</t>
+          <t>A 7575-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46107</v>
+        <v>45705</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15401-2026</t>
+          <t>A 55273-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6332,14 +6332,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46106</v>
+        <v>45968</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6395,7 +6395,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51157-2023</t>
+          <t>A 29697-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45219</v>
+        <v>45107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6468,7 +6468,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40053-2023</t>
+          <t>A 1551-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45168</v>
+        <v>44573</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6541,7 +6541,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55273-2025</t>
+          <t>A 13108-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45968</v>
+        <v>45002</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 27513-2025</t>
+          <t>A 69563-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45813</v>
+        <v>44532</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6687,7 +6687,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5630-2023</t>
+          <t>A 15401-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6697,14 +6697,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44960</v>
+        <v>46106</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6760,7 +6760,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11697-2024</t>
+          <t>A 60432-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45373</v>
+        <v>44911</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6833,7 +6833,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41725-2024</t>
+          <t>A 15700-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45560</v>
+        <v>46107</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6906,7 +6906,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56558-2024</t>
+          <t>A 15704-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6920,10 +6920,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45625</v>
+        <v>46107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6979,7 +6979,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25439-2022</t>
+          <t>A 56558-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44732</v>
+        <v>45625</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7052,7 +7052,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25726-2022</t>
+          <t>A 15698-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44733</v>
+        <v>46107</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>45754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60323-2025</t>
+          <t>A 25726-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7212,10 +7212,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45994</v>
+        <v>44733</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47334-2024</t>
+          <t>A 60323-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45587</v>
+        <v>45994</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7344,7 +7344,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15480-2025</t>
+          <t>A 41725-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45747</v>
+        <v>45560</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7417,7 +7417,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61741-2025</t>
+          <t>A 15480-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46002</v>
+        <v>45747</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7490,7 +7490,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41318-2022</t>
+          <t>A 61737-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44826</v>
+        <v>46002</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11.5</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7563,7 +7563,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7356-2025</t>
+          <t>A 29696-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45704</v>
+        <v>45107</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7636,7 +7636,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9492-2025</t>
+          <t>A 61741-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45715</v>
+        <v>46002</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7709,7 +7709,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16509-2025</t>
+          <t>A 47350-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7723,10 +7723,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45751</v>
+        <v>45587</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7782,7 +7782,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61737-2025</t>
+          <t>A 72891-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46002</v>
+        <v>44547</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7855,7 +7855,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 72891-2021</t>
+          <t>A 5987-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44547</v>
+        <v>45336</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7928,7 +7928,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20727-2023</t>
+          <t>A 41318-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45058</v>
+        <v>44826</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>11.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34665-2023</t>
+          <t>A 16509-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45140</v>
+        <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8074,7 +8074,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 69563-2021</t>
+          <t>A 39761-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8088,10 +8088,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44532</v>
+        <v>45167</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8147,7 +8147,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9785-2026</t>
+          <t>A 39762-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8161,10 +8161,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46072</v>
+        <v>45167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8220,7 +8220,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35404-2025</t>
+          <t>A 52043-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8234,10 +8234,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45855</v>
+        <v>45608</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8293,7 +8293,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2946-2024</t>
+          <t>A 47334-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8307,10 +8307,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45315</v>
+        <v>45587</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8366,7 +8366,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12090-2024</t>
+          <t>A 14183-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8380,10 +8380,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45377</v>
+        <v>45393</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8439,7 +8439,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 52043-2024</t>
+          <t>A 9785-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8453,10 +8453,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45608</v>
+        <v>46072</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8512,7 +8512,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57269-2024</t>
+          <t>A 4433-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45629</v>
+        <v>45686</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29697-2023</t>
+          <t>A 2946-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45107</v>
+        <v>45315</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8658,7 +8658,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 23492-2022</t>
+          <t>A 4315-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44721</v>
+        <v>45324</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8731,7 +8731,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 39761-2023</t>
+          <t>A 5985-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45167</v>
+        <v>45336</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8804,7 +8804,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46798-2024</t>
+          <t>A 35404-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45583</v>
+        <v>45855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8877,7 +8877,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30846-2026</t>
+          <t>A 23492-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46212</v>
+        <v>44721</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8950,7 +8950,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30869-2026</t>
+          <t>A 64560-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46212</v>
+        <v>45281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.3</v>
+        <v>7.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9023,7 +9023,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 65080-2023</t>
+          <t>A 3753-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9033,14 +9033,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45287</v>
+        <v>45321</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9096,7 +9096,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 3753-2024</t>
+          <t>A 1807-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45321</v>
+        <v>45307</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9169,7 +9169,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1807-2024</t>
+          <t>A 25439-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9183,10 +9183,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45307</v>
+        <v>44732</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9242,7 +9242,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31521-2026</t>
+          <t>A 5630-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46223</v>
+        <v>44960</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9315,7 +9315,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 31631-2026</t>
+          <t>A 51127-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9329,10 +9329,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46225</v>
+        <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 31641-2026</t>
+          <t>A 51130-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9398,14 +9398,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46225</v>
+        <v>45219</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 59711-2022</t>
+          <t>A 2605-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44908</v>
+        <v>45313</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 39762-2023</t>
+          <t>A 30869-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45167</v>
+        <v>46212</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9607,7 +9607,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 36502-2026</t>
+          <t>A 30846-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46269</v>
+        <v>46212</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9680,7 +9680,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61874-2024</t>
+          <t>A 34665-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45651</v>
+        <v>45140</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9753,7 +9753,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 31825-2026</t>
+          <t>A 32866-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9767,10 +9767,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46230</v>
+        <v>44784</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9826,7 +9826,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 32379-2026</t>
+          <t>A 65080-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9836,14 +9836,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46238</v>
+        <v>45287</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9899,7 +9899,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 32377-2026</t>
+          <t>A 31521-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9913,10 +9913,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9972,7 +9972,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 32378-2026</t>
+          <t>A 31631-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9986,10 +9986,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10045,7 +10045,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 25499-2022</t>
+          <t>A 31641-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10055,14 +10055,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44732</v>
+        <v>46225</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 32866-2022</t>
+          <t>A 59711-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10132,10 +10132,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44784</v>
+        <v>44908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10191,7 +10191,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 5985-2024</t>
+          <t>A 31825-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10205,10 +10205,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45336</v>
+        <v>46230</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10264,7 +10264,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 64291-2023</t>
+          <t>A 36502-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10278,10 +10278,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45280</v>
+        <v>46269</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10337,7 +10337,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 47350-2024</t>
+          <t>A 32379-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45587</v>
+        <v>46238</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10410,7 +10410,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 4315-2024</t>
+          <t>A 32377-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45324</v>
+        <v>46238</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10483,7 +10483,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1551-2022</t>
+          <t>A 32378-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44573</v>
+        <v>46238</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10556,7 +10556,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 51012-2023</t>
+          <t>A 12090-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45218</v>
+        <v>45377</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10585,13 +10585,8 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10634,7 +10629,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56832-2023</t>
+          <t>A 20727-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10648,10 +10643,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45244</v>
+        <v>45058</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10664,7 +10659,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10707,7 +10702,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 60432-2022</t>
+          <t>A 55071-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10717,14 +10712,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44911</v>
+        <v>45237</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10737,7 +10732,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10780,7 +10775,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 13108-2023</t>
+          <t>A 52166-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10794,10 +10789,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45002</v>
+        <v>45224</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10810,7 +10805,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10853,7 +10848,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 29696-2023</t>
+          <t>A 56832-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10867,10 +10862,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45107</v>
+        <v>45244</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10883,7 +10878,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10926,7 +10921,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 40751-2026</t>
+          <t>A 12091-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10940,10 +10935,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46296</v>
+        <v>45377</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10956,7 +10951,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10999,7 +10994,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 5987-2024</t>
+          <t>A 40559-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11013,10 +11008,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45336</v>
+        <v>46295</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11029,7 +11024,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11072,7 +11067,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 55071-2023</t>
+          <t>A 51012-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11082,14 +11077,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45237</v>
+        <v>45218</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11101,8 +11096,13 @@
           <t>HÄRRYDA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11145,7 +11145,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 40559-2026</t>
+          <t>A 64291-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11159,10 +11159,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46295</v>
+        <v>45280</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11218,7 +11218,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 51154-2023</t>
+          <t>A 40751-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11232,10 +11232,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45219</v>
+        <v>46296</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11291,7 +11291,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 52166-2023</t>
+          <t>A 25499-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11305,10 +11305,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45224</v>
+        <v>44732</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11364,7 +11364,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 22271-2025</t>
+          <t>A 46798-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11378,10 +11378,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45785</v>
+        <v>45583</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45811</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>46105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45968</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45715</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>44796</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>46190</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45239</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>45813</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>46163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>45224</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>46294</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44732</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44494</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44615</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>44784</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44543</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>44694</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44508</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>44873</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45219</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45785</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45704</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45715</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45715</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45895</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45895</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>45629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>45012</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45798</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45925</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45936</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45934</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45168</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>45811</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45950</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>45813</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>45373</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>46098</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>45705</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>45968</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>45107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44573</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>45002</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44532</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>46106</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>44911</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>46107</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>46107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>45625</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>46107</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>44733</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45994</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>45560</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>45747</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>46002</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>45107</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>46002</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>45587</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44547</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>45336</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44826</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>45167</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>45167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>45608</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>45587</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45393</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>46072</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>45686</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45315</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45324</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>45336</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>45855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>44721</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>45281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>45321</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>45307</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>44732</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44960</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>45219</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>45313</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>46212</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>46212</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45140</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44784</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>45287</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>46223</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>46225</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>46225</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>44908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>46230</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>46269</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>46238</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>46238</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>46238</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45377</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45058</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45237</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>45224</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45244</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>45377</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>46295</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>45218</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>45280</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>46296</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>44732</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>45583</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45811</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>46105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45968</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45715</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>44796</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>46190</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>43998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>44902</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>45175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45239</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>45813</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>46163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>45224</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>46294</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44732</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>44708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44494</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44615</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>44784</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44543</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>44694</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44508</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>44873</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45219</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45785</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45704</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45715</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45715</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45895</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45895</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>45629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>45012</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45798</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45925</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45936</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45934</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45168</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>45811</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45950</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>45813</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>45373</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>46098</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>45705</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>45968</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>45107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44573</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>45002</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44532</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>46106</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>44911</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>46107</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>46107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>45625</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>46107</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>44733</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45994</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>45560</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>45747</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>46002</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>45107</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>46002</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>45587</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44547</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>45336</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44826</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>45167</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>45167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>45608</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>45587</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45393</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>46072</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>45686</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45315</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45324</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>45336</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>45855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>44721</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>45281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>45321</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>45307</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>44732</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44960</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>45219</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>45313</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>46212</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>46212</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45140</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44784</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>45287</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>46223</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>46225</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>46225</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>44908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>46230</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>46269</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>46238</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>46238</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>46238</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45377</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45058</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45237</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>45224</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45244</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>45377</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>46295</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>45218</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>45280</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>46296</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>44732</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>45583</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>

--- a/Översikt HÄRRYDA.xlsx
+++ b/Översikt HÄRRYDA.xlsx
@@ -601,7 +601,7 @@
         <v>45061</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45608</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45567</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45030</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45057</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44732</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>44508</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37201-2023</t>
+          <t>A 26989-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45155</v>
+        <v>45811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1407,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1422,1115 +1422,1121 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Nötkråka
+Kungsfågel
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37201-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sexfläckig bastardsvärmare
 Slåttergubbe
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 37201-2023 artfynd.xlsx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 37201-2023 karta.png", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 37201-2023 georefererad karta.tif", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 37201-2023 FSC-klagomål.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 37201-2023 FSC-klagomål mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 37201-2023 tillsynsbegäran.docx", "A 37201-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 37201-2023 tillsynsbegäran mail.docx", "A 37201-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 55708-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45239</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>5.4</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Talltita
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55708-2023 artfynd.xlsx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55708-2023 karta.png", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55708-2023 georefererad karta.tif", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55708-2023 FSC-klagomål.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55708-2023 FSC-klagomål mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55708-2023 tillsynsbegäran.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55708-2023 tillsynsbegäran mail.docx", "A 55708-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 55708-2023 prioriterade fågelarter.docx", "A 55708-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 26989-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45811</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 15249-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Kornknutmossa
+Smal svampklubba
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S 2595-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>4.6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J13" t="n">
         <v>3</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Nötkråka
 Kungsfågel
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 26989-2025 artfynd.xlsx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 26989-2025 karta.png", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 26989-2025 georefererad karta.tif", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 26989-2025 FSC-klagomål.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 26989-2025 FSC-klagomål mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 26989-2025 tillsynsbegäran.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 26989-2025 tillsynsbegäran mail.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/A 26989-2025 prioriterade fågelarter.docx", "A 26989-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 15249-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Kornknutmossa
-Smal svampklubba
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 15249-2026 artfynd.xlsx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 15249-2026 karta.png", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 15249-2026 georefererad karta.tif", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 15249-2026 FSC-klagomål.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 15249-2026 FSC-klagomål mail.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 15249-2026 tillsynsbegäran.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 15249-2026 tillsynsbegäran mail.docx", "A 15249-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/S 2595-2026 artfynd.xlsx", "S 2595-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/S 2595-2026 karta.png", "S 2595-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/S 2595-2026 georefererad karta.tif", "S 2595-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/S 2595-2026 FSC-klagomål.docx", "S 2595-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/S 2595-2026 FSC-klagomål mail.docx", "S 2595-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/S 2595-2026 tillsynsbegäran.docx", "S 2595-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/S 2595-2026 tillsynsbegäran mail.docx", "S 2595-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/fåglar/S 2595-2026 prioriterade fågelarter.docx", "S 2595-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9491-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45715</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 9491-2025 artfynd.xlsx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 9491-2025 karta.png", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 9491-2025 georefererad karta.tif", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 9491-2025 FSC-klagomål.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 9491-2025 FSC-klagomål mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 9491-2025 tillsynsbegäran.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 9491-2025 tillsynsbegäran mail.docx", "A 9491-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 55274-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Skuggmossa
+Trådticka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/artfynd/A 55274-2025 artfynd.xlsx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor/A 55274-2025 karta.png", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/kartor_geotiff/A 55274-2025 georefererad karta.tif", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomål/A 55274-2025 FSC-klagomål.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/klagomålsmail/A 55274-2025 FSC-klagomål mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsyn/A 55274-2025 tillsynsbegäran.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1401/tillsynsmail/A 55274-2025 tillsynsbegäran mail.docx", "A 55274-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 63592-2021</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>44508</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HÄRRYDA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRRYDA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="